--- a/RESULTS/tables/facility_missingness_external.xlsx
+++ b/RESULTS/tables/facility_missingness_external.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,17 +417,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Facility</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Overall Missing Percent</t>
         </is>
@@ -447,10 +435,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1698</v>
+        <v>5402</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>0.723404255319149</v>
@@ -458,7 +446,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1719</v>
+        <v>3069</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -469,7 +457,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>459</v>
+        <v>3068</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -480,7 +468,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -491,7 +479,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3068</v>
+        <v>459</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -502,7 +490,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1668</v>
+        <v>3067</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -524,7 +512,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3067</v>
+        <v>1570</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -535,7 +523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3066</v>
+        <v>1668</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -546,10 +534,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1716</v>
+        <v>1698</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>0.723404255319149</v>
@@ -557,7 +545,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5402</v>
+        <v>1719</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -568,7 +556,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1570</v>
+        <v>1716</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -590,7 +578,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1694</v>
+        <v>3047</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
@@ -601,7 +589,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1700</v>
+        <v>1859</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
@@ -612,7 +600,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1641</v>
+        <v>597</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
@@ -623,7 +611,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1697</v>
+        <v>1659</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
@@ -634,7 +622,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
@@ -656,7 +644,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1692</v>
+        <v>1695</v>
       </c>
       <c r="B21" t="n">
         <v>1</v>
@@ -667,7 +655,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1621</v>
+        <v>1692</v>
       </c>
       <c r="B22" t="n">
         <v>1</v>
@@ -678,7 +666,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1622</v>
+        <v>1700</v>
       </c>
       <c r="B23" t="n">
         <v>1</v>
@@ -689,7 +677,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="B24" t="n">
         <v>1</v>
@@ -700,7 +688,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1623</v>
+        <v>1080</v>
       </c>
       <c r="B25" t="n">
         <v>1</v>
@@ -711,7 +699,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1624</v>
+        <v>115</v>
       </c>
       <c r="B26" t="n">
         <v>1</v>
@@ -722,7 +710,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1859</v>
+        <v>121</v>
       </c>
       <c r="B27" t="n">
         <v>1</v>
@@ -733,7 +721,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1659</v>
+        <v>116</v>
       </c>
       <c r="B28" t="n">
         <v>1</v>
@@ -744,10 +732,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1629</v>
+        <v>119</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
         <v>0.6595744680851063</v>
@@ -755,7 +743,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>597</v>
+        <v>149</v>
       </c>
       <c r="B30" t="n">
         <v>1</v>
@@ -766,7 +754,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1080</v>
+        <v>1697</v>
       </c>
       <c r="B31" t="n">
         <v>1</v>
@@ -777,7 +765,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1589</v>
+        <v>1713</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
@@ -788,7 +776,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3047</v>
+        <v>1641</v>
       </c>
       <c r="B33" t="n">
         <v>1</v>
@@ -799,7 +787,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>116</v>
+        <v>1621</v>
       </c>
       <c r="B34" t="n">
         <v>1</v>
@@ -810,7 +798,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1736</v>
+        <v>5532</v>
       </c>
       <c r="B35" t="n">
         <v>1</v>
@@ -821,7 +809,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5532</v>
+        <v>1629</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -832,7 +820,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118</v>
+        <v>1624</v>
       </c>
       <c r="B37" t="n">
         <v>1</v>
@@ -843,10 +831,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119</v>
+        <v>1623</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
         <v>0.6595744680851063</v>
@@ -854,7 +842,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115</v>
+        <v>1736</v>
       </c>
       <c r="B39" t="n">
         <v>1</v>
@@ -865,7 +853,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1713</v>
+        <v>1622</v>
       </c>
       <c r="B40" t="n">
         <v>1</v>
@@ -876,7 +864,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121</v>
+        <v>1589</v>
       </c>
       <c r="B41" t="n">
         <v>1</v>
@@ -898,7 +886,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5200</v>
+        <v>531</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
@@ -909,7 +897,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>531</v>
+        <v>5200</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
@@ -931,7 +919,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1711</v>
+        <v>1662</v>
       </c>
       <c r="B46" t="n">
         <v>2</v>
@@ -942,7 +930,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1662</v>
+        <v>1711</v>
       </c>
       <c r="B47" t="n">
         <v>2</v>
@@ -964,10 +952,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1591</v>
+        <v>1690</v>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
         <v>0.5319148936170213</v>
@@ -975,10 +963,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117</v>
+        <v>1591</v>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C50" t="n">
         <v>0.5319148936170213</v>
@@ -986,10 +974,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1690</v>
+        <v>117</v>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="n">
         <v>0.5319148936170213</v>
@@ -997,7 +985,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1606</v>
+        <v>1649</v>
       </c>
       <c r="B52" t="n">
         <v>2</v>
@@ -1008,7 +996,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>110</v>
+        <v>1606</v>
       </c>
       <c r="B53" t="n">
         <v>2</v>
@@ -1019,7 +1007,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1649</v>
+        <v>112</v>
       </c>
       <c r="B54" t="n">
         <v>2</v>
@@ -1030,7 +1018,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B55" t="n">
         <v>2</v>
@@ -1041,10 +1029,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>114</v>
+        <v>1576</v>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C56" t="n">
         <v>0.5</v>
@@ -1052,10 +1040,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1576</v>
+        <v>110</v>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C57" t="n">
         <v>0.5</v>
@@ -1063,10 +1051,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1656</v>
+        <v>1820</v>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" t="n">
         <v>0.4680851063829787</v>
@@ -1074,7 +1062,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1855</v>
+        <v>1816</v>
       </c>
       <c r="B59" t="n">
         <v>1</v>
@@ -1085,10 +1073,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1638</v>
+        <v>1849</v>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
         <v>0.4680851063829787</v>
@@ -1096,10 +1084,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1642</v>
+        <v>4405</v>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
         <v>0.4680851063829787</v>
@@ -1107,10 +1095,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1683</v>
+        <v>3781</v>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
         <v>0.4680851063829787</v>
@@ -1118,7 +1106,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1710</v>
+        <v>1706</v>
       </c>
       <c r="B63" t="n">
         <v>2</v>
@@ -1129,7 +1117,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1685</v>
+        <v>1614</v>
       </c>
       <c r="B64" t="n">
         <v>2</v>
@@ -1140,10 +1128,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>3781</v>
+        <v>1642</v>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65" t="n">
         <v>0.4680851063829787</v>
@@ -1151,10 +1139,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1820</v>
+        <v>1638</v>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66" t="n">
         <v>0.4680851063829787</v>
@@ -1162,10 +1150,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1816</v>
+        <v>1710</v>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67" t="n">
         <v>0.4680851063829787</v>
@@ -1173,7 +1161,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1706</v>
+        <v>1685</v>
       </c>
       <c r="B68" t="n">
         <v>2</v>
@@ -1184,7 +1172,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1614</v>
+        <v>1683</v>
       </c>
       <c r="B69" t="n">
         <v>2</v>
@@ -1195,10 +1183,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1849</v>
+        <v>1656</v>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
         <v>0.4680851063829787</v>
@@ -1206,7 +1194,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4405</v>
+        <v>1855</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -1239,7 +1227,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1709</v>
+        <v>1651</v>
       </c>
       <c r="B74" t="n">
         <v>2</v>
@@ -1250,7 +1238,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1703</v>
+        <v>1654</v>
       </c>
       <c r="B75" t="n">
         <v>2</v>
@@ -1261,7 +1249,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1707</v>
+        <v>1458</v>
       </c>
       <c r="B76" t="n">
         <v>2</v>
@@ -1272,7 +1260,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1660</v>
+        <v>1682</v>
       </c>
       <c r="B77" t="n">
         <v>2</v>
@@ -1283,7 +1271,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1651</v>
+        <v>1612</v>
       </c>
       <c r="B78" t="n">
         <v>2</v>
@@ -1294,7 +1282,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1654</v>
+        <v>1703</v>
       </c>
       <c r="B79" t="n">
         <v>2</v>
@@ -1305,7 +1293,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1712</v>
+        <v>1635</v>
       </c>
       <c r="B80" t="n">
         <v>2</v>
@@ -1316,7 +1304,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1682</v>
+        <v>1633</v>
       </c>
       <c r="B81" t="n">
         <v>2</v>
@@ -1327,7 +1315,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1705</v>
+        <v>1631</v>
       </c>
       <c r="B82" t="n">
         <v>2</v>
@@ -1338,7 +1326,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1635</v>
+        <v>1712</v>
       </c>
       <c r="B83" t="n">
         <v>2</v>
@@ -1349,7 +1337,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1593</v>
+        <v>1705</v>
       </c>
       <c r="B84" t="n">
         <v>2</v>
@@ -1360,7 +1348,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1633</v>
+        <v>1709</v>
       </c>
       <c r="B85" t="n">
         <v>2</v>
@@ -1371,7 +1359,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1610</v>
+        <v>1707</v>
       </c>
       <c r="B86" t="n">
         <v>2</v>
@@ -1382,7 +1370,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1458</v>
+        <v>1565</v>
       </c>
       <c r="B87" t="n">
         <v>2</v>
@@ -1393,7 +1381,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1583</v>
+        <v>1660</v>
       </c>
       <c r="B88" t="n">
         <v>2</v>
@@ -1404,7 +1392,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1631</v>
+        <v>1583</v>
       </c>
       <c r="B89" t="n">
         <v>2</v>
@@ -1415,7 +1403,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1612</v>
+        <v>1593</v>
       </c>
       <c r="B90" t="n">
         <v>2</v>
@@ -1426,7 +1414,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1569</v>
+        <v>1610</v>
       </c>
       <c r="B91" t="n">
         <v>2</v>
@@ -1437,7 +1425,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="B92" t="n">
         <v>2</v>
@@ -1481,7 +1469,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1980</v>
+        <v>4361</v>
       </c>
       <c r="B96" t="n">
         <v>1</v>
@@ -1492,7 +1480,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1937</v>
+        <v>3856</v>
       </c>
       <c r="B97" t="n">
         <v>1</v>
@@ -1503,7 +1491,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4361</v>
+        <v>450</v>
       </c>
       <c r="B98" t="n">
         <v>1</v>
@@ -1514,10 +1502,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>237</v>
+        <v>439</v>
       </c>
       <c r="B99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
         <v>0.4042553191489361</v>
@@ -1525,7 +1513,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4364</v>
+        <v>123</v>
       </c>
       <c r="B100" t="n">
         <v>1</v>
@@ -1536,7 +1524,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4384</v>
+        <v>5279</v>
       </c>
       <c r="B101" t="n">
         <v>1</v>
@@ -1547,7 +1535,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>123</v>
+        <v>4391</v>
       </c>
       <c r="B102" t="n">
         <v>1</v>
@@ -1558,7 +1546,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>5279</v>
+        <v>1940</v>
       </c>
       <c r="B103" t="n">
         <v>1</v>
@@ -1569,7 +1557,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1717</v>
+        <v>1923</v>
       </c>
       <c r="B104" t="n">
         <v>1</v>
@@ -1580,7 +1568,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>3856</v>
+        <v>1937</v>
       </c>
       <c r="B105" t="n">
         <v>1</v>
@@ -1591,7 +1579,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2166</v>
+        <v>1924</v>
       </c>
       <c r="B106" t="n">
         <v>1</v>
@@ -1602,7 +1590,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>5278</v>
+        <v>4384</v>
       </c>
       <c r="B107" t="n">
         <v>1</v>
@@ -1613,7 +1601,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1940</v>
+        <v>4364</v>
       </c>
       <c r="B108" t="n">
         <v>1</v>
@@ -1624,7 +1612,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>4391</v>
+        <v>3805</v>
       </c>
       <c r="B109" t="n">
         <v>1</v>
@@ -1635,7 +1623,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1924</v>
+        <v>1980</v>
       </c>
       <c r="B110" t="n">
         <v>1</v>
@@ -1646,10 +1634,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>447</v>
+        <v>237</v>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111" t="n">
         <v>0.4042553191489361</v>
@@ -1657,7 +1645,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>3805</v>
+        <v>447</v>
       </c>
       <c r="B112" t="n">
         <v>1</v>
@@ -1668,7 +1656,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>439</v>
+        <v>5439</v>
       </c>
       <c r="B113" t="n">
         <v>1</v>
@@ -1679,7 +1667,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>5439</v>
+        <v>5278</v>
       </c>
       <c r="B114" t="n">
         <v>1</v>
@@ -1690,7 +1678,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1923</v>
+        <v>1646</v>
       </c>
       <c r="B115" t="n">
         <v>1</v>
@@ -1701,7 +1689,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1646</v>
+        <v>1717</v>
       </c>
       <c r="B116" t="n">
         <v>1</v>
@@ -1712,7 +1700,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>450</v>
+        <v>2166</v>
       </c>
       <c r="B117" t="n">
         <v>1</v>
@@ -1745,7 +1733,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1645</v>
+        <v>1577</v>
       </c>
       <c r="B120" t="n">
         <v>3</v>
@@ -1756,7 +1744,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1640</v>
+        <v>1609</v>
       </c>
       <c r="B121" t="n">
         <v>3</v>
@@ -1767,7 +1755,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1702</v>
+        <v>1640</v>
       </c>
       <c r="B122" t="n">
         <v>3</v>
@@ -1778,7 +1766,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1577</v>
+        <v>1645</v>
       </c>
       <c r="B123" t="n">
         <v>3</v>
@@ -1789,7 +1777,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1609</v>
+        <v>1702</v>
       </c>
       <c r="B124" t="n">
         <v>3</v>
@@ -1822,7 +1810,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1573</v>
+        <v>1454</v>
       </c>
       <c r="B127" t="n">
         <v>4</v>
@@ -1844,7 +1832,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1454</v>
+        <v>1573</v>
       </c>
       <c r="B129" t="n">
         <v>4</v>
@@ -1866,7 +1854,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1456</v>
+        <v>1644</v>
       </c>
       <c r="B131" t="n">
         <v>3</v>
@@ -1877,7 +1865,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1644</v>
+        <v>1456</v>
       </c>
       <c r="B132" t="n">
         <v>3</v>
@@ -1943,7 +1931,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B138" t="n">
         <v>2</v>
@@ -1954,10 +1942,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>111</v>
+        <v>1580</v>
       </c>
       <c r="B139" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C139" t="n">
         <v>0.3723404255319149</v>
@@ -1965,7 +1953,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1580</v>
+        <v>1550</v>
       </c>
       <c r="B140" t="n">
         <v>4</v>
@@ -1976,10 +1964,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1550</v>
+        <v>105</v>
       </c>
       <c r="B141" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C141" t="n">
         <v>0.3723404255319149</v>
@@ -1998,10 +1986,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1572</v>
+        <v>1452</v>
       </c>
       <c r="B143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C143" t="n">
         <v>0.3617021276595744</v>
@@ -2009,10 +1997,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1452</v>
+        <v>1572</v>
       </c>
       <c r="B144" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C144" t="n">
         <v>0.3617021276595744</v>
@@ -2196,10 +2184,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1582</v>
+        <v>365</v>
       </c>
       <c r="B161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C161" t="n">
         <v>0.3404255319148936</v>
@@ -2207,7 +2195,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>4366</v>
+        <v>325</v>
       </c>
       <c r="B162" t="n">
         <v>1</v>
@@ -2218,7 +2206,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1585</v>
+        <v>407</v>
       </c>
       <c r="B163" t="n">
         <v>1</v>
@@ -2229,10 +2217,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1597</v>
+        <v>437</v>
       </c>
       <c r="B164" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C164" t="n">
         <v>0.3404255319148936</v>
@@ -2240,7 +2228,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2745</v>
+        <v>134</v>
       </c>
       <c r="B165" t="n">
         <v>1</v>
@@ -2251,10 +2239,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1615</v>
+        <v>12000</v>
       </c>
       <c r="B166" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C166" t="n">
         <v>0.3404255319148936</v>
@@ -2262,7 +2250,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>3811</v>
+        <v>5450</v>
       </c>
       <c r="B167" t="n">
         <v>1</v>
@@ -2273,10 +2261,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1461</v>
+        <v>5452</v>
       </c>
       <c r="B168" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C168" t="n">
         <v>0.3404255319148936</v>
@@ -2284,7 +2272,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>3804</v>
+        <v>5290</v>
       </c>
       <c r="B169" t="n">
         <v>1</v>
@@ -2295,7 +2283,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1619</v>
+        <v>5359</v>
       </c>
       <c r="B170" t="n">
         <v>1</v>
@@ -2306,10 +2294,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1444</v>
+        <v>5296</v>
       </c>
       <c r="B171" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C171" t="n">
         <v>0.3404255319148936</v>
@@ -2317,10 +2305,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1579</v>
+        <v>5326</v>
       </c>
       <c r="B172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C172" t="n">
         <v>0.3404255319148936</v>
@@ -2328,10 +2316,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1575</v>
+        <v>5281</v>
       </c>
       <c r="B173" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C173" t="n">
         <v>0.3404255319148936</v>
@@ -2339,7 +2327,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1571</v>
+        <v>5335</v>
       </c>
       <c r="B174" t="n">
         <v>1</v>
@@ -2350,7 +2338,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1478</v>
+        <v>454</v>
       </c>
       <c r="B175" t="n">
         <v>1</v>
@@ -2361,7 +2349,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1911</v>
+        <v>455</v>
       </c>
       <c r="B176" t="n">
         <v>1</v>
@@ -2372,7 +2360,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2743</v>
+        <v>456</v>
       </c>
       <c r="B177" t="n">
         <v>1</v>
@@ -2383,10 +2371,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1349</v>
+        <v>5147</v>
       </c>
       <c r="B178" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C178" t="n">
         <v>0.3404255319148936</v>
@@ -2394,10 +2382,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1337</v>
+        <v>5273</v>
       </c>
       <c r="B179" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C179" t="n">
         <v>0.3404255319148936</v>
@@ -2405,7 +2393,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1948</v>
+        <v>5274</v>
       </c>
       <c r="B180" t="n">
         <v>1</v>
@@ -2416,7 +2404,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1826</v>
+        <v>5276</v>
       </c>
       <c r="B181" t="n">
         <v>1</v>
@@ -2427,7 +2415,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1950</v>
+        <v>452</v>
       </c>
       <c r="B182" t="n">
         <v>1</v>
@@ -2438,7 +2426,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1958</v>
+        <v>444</v>
       </c>
       <c r="B183" t="n">
         <v>1</v>
@@ -2449,7 +2437,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1821</v>
+        <v>446</v>
       </c>
       <c r="B184" t="n">
         <v>1</v>
@@ -2460,7 +2448,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1981</v>
+        <v>448</v>
       </c>
       <c r="B185" t="n">
         <v>1</v>
@@ -2471,7 +2459,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>1814</v>
+        <v>451</v>
       </c>
       <c r="B186" t="n">
         <v>1</v>
@@ -2482,7 +2470,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>2712</v>
+        <v>453</v>
       </c>
       <c r="B187" t="n">
         <v>1</v>
@@ -2493,7 +2481,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1993</v>
+        <v>441</v>
       </c>
       <c r="B188" t="n">
         <v>1</v>
@@ -2504,7 +2492,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>2002</v>
+        <v>443</v>
       </c>
       <c r="B189" t="n">
         <v>1</v>
@@ -2515,7 +2503,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>2095</v>
+        <v>530</v>
       </c>
       <c r="B190" t="n">
         <v>1</v>
@@ -2526,7 +2514,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1740</v>
+        <v>1814</v>
       </c>
       <c r="B191" t="n">
         <v>1</v>
@@ -2537,7 +2525,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>2697</v>
+        <v>1821</v>
       </c>
       <c r="B192" t="n">
         <v>1</v>
@@ -2548,7 +2536,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2698</v>
+        <v>1826</v>
       </c>
       <c r="B193" t="n">
         <v>1</v>
@@ -2559,7 +2547,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>1735</v>
+        <v>1911</v>
       </c>
       <c r="B194" t="n">
         <v>1</v>
@@ -2570,7 +2558,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2733</v>
+        <v>1981</v>
       </c>
       <c r="B195" t="n">
         <v>1</v>
@@ -2581,10 +2569,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>1523</v>
+        <v>1958</v>
       </c>
       <c r="B196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C196" t="n">
         <v>0.3404255319148936</v>
@@ -2592,7 +2580,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>407</v>
+        <v>1950</v>
       </c>
       <c r="B197" t="n">
         <v>1</v>
@@ -2603,7 +2591,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>444</v>
+        <v>2698</v>
       </c>
       <c r="B198" t="n">
         <v>1</v>
@@ -2614,7 +2602,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>5450</v>
+        <v>2697</v>
       </c>
       <c r="B199" t="n">
         <v>1</v>
@@ -2625,7 +2613,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>441</v>
+        <v>2095</v>
       </c>
       <c r="B200" t="n">
         <v>1</v>
@@ -2636,7 +2624,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>5276</v>
+        <v>1993</v>
       </c>
       <c r="B201" t="n">
         <v>1</v>
@@ -2647,7 +2635,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>5274</v>
+        <v>2002</v>
       </c>
       <c r="B202" t="n">
         <v>1</v>
@@ -2658,7 +2646,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>437</v>
+        <v>1948</v>
       </c>
       <c r="B203" t="n">
         <v>1</v>
@@ -2669,10 +2657,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>5273</v>
+        <v>2743</v>
       </c>
       <c r="B204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C204" t="n">
         <v>0.3404255319148936</v>
@@ -2680,7 +2668,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>5147</v>
+        <v>2733</v>
       </c>
       <c r="B205" t="n">
         <v>1</v>
@@ -2691,7 +2679,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>5452</v>
+        <v>2712</v>
       </c>
       <c r="B206" t="n">
         <v>1</v>
@@ -2702,7 +2690,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>4433</v>
+        <v>4366</v>
       </c>
       <c r="B207" t="n">
         <v>1</v>
@@ -2713,7 +2701,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>5461</v>
+        <v>4401</v>
       </c>
       <c r="B208" t="n">
         <v>1</v>
@@ -2724,7 +2712,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>5463</v>
+        <v>477</v>
       </c>
       <c r="B209" t="n">
         <v>1</v>
@@ -2735,7 +2723,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>365</v>
+        <v>496</v>
       </c>
       <c r="B210" t="n">
         <v>1</v>
@@ -2746,7 +2734,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>325</v>
+        <v>4433</v>
       </c>
       <c r="B211" t="n">
         <v>1</v>
@@ -2757,7 +2745,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>5472</v>
+        <v>4417</v>
       </c>
       <c r="B212" t="n">
         <v>1</v>
@@ -2768,7 +2756,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>177</v>
+        <v>4412</v>
       </c>
       <c r="B213" t="n">
         <v>1</v>
@@ -2779,7 +2767,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>443</v>
+        <v>4406</v>
       </c>
       <c r="B214" t="n">
         <v>1</v>
@@ -2790,7 +2778,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>446</v>
+        <v>2745</v>
       </c>
       <c r="B215" t="n">
         <v>1</v>
@@ -2801,7 +2789,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>4412</v>
+        <v>3811</v>
       </c>
       <c r="B216" t="n">
         <v>1</v>
@@ -2812,7 +2800,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>448</v>
+        <v>3804</v>
       </c>
       <c r="B217" t="n">
         <v>1</v>
@@ -2823,7 +2811,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>5381</v>
+        <v>140</v>
       </c>
       <c r="B218" t="n">
         <v>1</v>
@@ -2834,7 +2822,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>5407</v>
+        <v>5438</v>
       </c>
       <c r="B219" t="n">
         <v>1</v>
@@ -2845,7 +2833,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>5425</v>
+        <v>11997</v>
       </c>
       <c r="B220" t="n">
         <v>1</v>
@@ -2856,7 +2844,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>5438</v>
+        <v>5425</v>
       </c>
       <c r="B221" t="n">
         <v>1</v>
@@ -2867,7 +2855,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>530</v>
+        <v>5407</v>
       </c>
       <c r="B222" t="n">
         <v>1</v>
@@ -2878,7 +2866,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>496</v>
+        <v>5381</v>
       </c>
       <c r="B223" t="n">
         <v>1</v>
@@ -2889,7 +2877,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>477</v>
+        <v>177</v>
       </c>
       <c r="B224" t="n">
         <v>1</v>
@@ -2900,10 +2888,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>5281</v>
+        <v>1735</v>
       </c>
       <c r="B225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C225" t="n">
         <v>0.3404255319148936</v>
@@ -2911,7 +2899,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>456</v>
+        <v>1740</v>
       </c>
       <c r="B226" t="n">
         <v>1</v>
@@ -2922,10 +2910,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>455</v>
+        <v>1216</v>
       </c>
       <c r="B227" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C227" t="n">
         <v>0.3404255319148936</v>
@@ -2933,7 +2921,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>454</v>
+        <v>1619</v>
       </c>
       <c r="B228" t="n">
         <v>1</v>
@@ -2944,10 +2932,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>453</v>
+        <v>1615</v>
       </c>
       <c r="B229" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C229" t="n">
         <v>0.3404255319148936</v>
@@ -2955,10 +2943,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>452</v>
+        <v>1597</v>
       </c>
       <c r="B230" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C230" t="n">
         <v>0.3404255319148936</v>
@@ -2966,7 +2954,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>451</v>
+        <v>1571</v>
       </c>
       <c r="B231" t="n">
         <v>1</v>
@@ -2977,10 +2965,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>5335</v>
+        <v>1575</v>
       </c>
       <c r="B232" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C232" t="n">
         <v>0.3404255319148936</v>
@@ -2988,10 +2976,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>4417</v>
+        <v>1582</v>
       </c>
       <c r="B233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C233" t="n">
         <v>0.3404255319148936</v>
@@ -2999,10 +2987,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>5359</v>
+        <v>1579</v>
       </c>
       <c r="B234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C234" t="n">
         <v>0.3404255319148936</v>
@@ -3010,7 +2998,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>108</v>
+        <v>1585</v>
       </c>
       <c r="B235" t="n">
         <v>1</v>
@@ -3021,10 +3009,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>5506</v>
+        <v>1461</v>
       </c>
       <c r="B236" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C236" t="n">
         <v>0.3404255319148936</v>
@@ -3032,10 +3020,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>5536</v>
+        <v>1523</v>
       </c>
       <c r="B237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C237" t="n">
         <v>0.3404255319148936</v>
@@ -3043,7 +3031,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>4401</v>
+        <v>1478</v>
       </c>
       <c r="B238" t="n">
         <v>1</v>
@@ -3054,10 +3042,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>5326</v>
+        <v>1337</v>
       </c>
       <c r="B239" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C239" t="n">
         <v>0.3404255319148936</v>
@@ -3065,10 +3053,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>11997</v>
+        <v>1349</v>
       </c>
       <c r="B240" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C240" t="n">
         <v>0.3404255319148936</v>
@@ -3076,10 +3064,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>5478</v>
+        <v>1444</v>
       </c>
       <c r="B241" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C241" t="n">
         <v>0.3404255319148936</v>
@@ -3087,7 +3075,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>5534</v>
+        <v>5536</v>
       </c>
       <c r="B242" t="n">
         <v>1</v>
@@ -3098,7 +3086,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>4406</v>
+        <v>5506</v>
       </c>
       <c r="B243" t="n">
         <v>1</v>
@@ -3109,7 +3097,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>12000</v>
+        <v>5478</v>
       </c>
       <c r="B244" t="n">
         <v>1</v>
@@ -3120,7 +3108,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>103</v>
+        <v>5534</v>
       </c>
       <c r="B245" t="n">
         <v>1</v>
@@ -3131,7 +3119,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>134</v>
+        <v>5514</v>
       </c>
       <c r="B246" t="n">
         <v>1</v>
@@ -3142,10 +3130,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>109</v>
+        <v>5472</v>
       </c>
       <c r="B247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C247" t="n">
         <v>0.3404255319148936</v>
@@ -3164,7 +3152,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>140</v>
+        <v>5461</v>
       </c>
       <c r="B249" t="n">
         <v>1</v>
@@ -3175,10 +3163,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1216</v>
+        <v>5463</v>
       </c>
       <c r="B250" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C250" t="n">
         <v>0.3404255319148936</v>
@@ -3186,10 +3174,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>5514</v>
+        <v>109</v>
       </c>
       <c r="B251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C251" t="n">
         <v>0.3404255319148936</v>
@@ -3197,7 +3185,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>5290</v>
+        <v>108</v>
       </c>
       <c r="B252" t="n">
         <v>1</v>
@@ -3219,7 +3207,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>5296</v>
+        <v>103</v>
       </c>
       <c r="B254" t="n">
         <v>1</v>
@@ -3230,10 +3218,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1446</v>
+        <v>1543</v>
       </c>
       <c r="B255" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C255" t="n">
         <v>0.3404255319148936</v>
@@ -3241,10 +3229,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>1495</v>
+        <v>1190</v>
       </c>
       <c r="B256" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C256" t="n">
         <v>0.3404255319148936</v>
@@ -3252,7 +3240,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>1470</v>
+        <v>1495</v>
       </c>
       <c r="B257" t="n">
         <v>3</v>
@@ -3263,10 +3251,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1155</v>
+        <v>1446</v>
       </c>
       <c r="B258" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C258" t="n">
         <v>0.3404255319148936</v>
@@ -3274,7 +3262,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1543</v>
+        <v>1470</v>
       </c>
       <c r="B259" t="n">
         <v>3</v>
@@ -3285,10 +3273,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1190</v>
+        <v>1155</v>
       </c>
       <c r="B260" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C260" t="n">
         <v>0.3404255319148936</v>
@@ -3549,7 +3537,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1602</v>
+        <v>1594</v>
       </c>
       <c r="B284" t="n">
         <v>4</v>
@@ -3560,10 +3548,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1594</v>
+        <v>1256</v>
       </c>
       <c r="B285" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C285" t="n">
         <v>0.324468085106383</v>
@@ -3582,10 +3570,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1256</v>
+        <v>1602</v>
       </c>
       <c r="B287" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C287" t="n">
         <v>0.324468085106383</v>
@@ -3637,10 +3625,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>1393</v>
+        <v>1254</v>
       </c>
       <c r="B292" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C292" t="n">
         <v>0.3212765957446808</v>
@@ -3648,10 +3636,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>1254</v>
+        <v>1393</v>
       </c>
       <c r="B293" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C293" t="n">
         <v>0.3212765957446808</v>
@@ -3747,10 +3735,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>1367</v>
+        <v>1394</v>
       </c>
       <c r="B302" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C302" t="n">
         <v>0.3191489361702127</v>
@@ -3758,10 +3746,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>1394</v>
+        <v>1367</v>
       </c>
       <c r="B303" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C303" t="n">
         <v>0.3191489361702127</v>
@@ -3835,10 +3823,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>1165</v>
+        <v>1227</v>
       </c>
       <c r="B310" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C310" t="n">
         <v>0.3148936170212766</v>
@@ -3846,10 +3834,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>1227</v>
+        <v>1165</v>
       </c>
       <c r="B311" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C311" t="n">
         <v>0.3148936170212766</v>
@@ -3868,10 +3856,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>1457</v>
+        <v>1224</v>
       </c>
       <c r="B313" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C313" t="n">
         <v>0.3148936170212765</v>
@@ -3879,10 +3867,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>1224</v>
+        <v>1457</v>
       </c>
       <c r="B314" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C314" t="n">
         <v>0.3148936170212765</v>
@@ -4088,10 +4076,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>1520</v>
+        <v>1390</v>
       </c>
       <c r="B333" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C333" t="n">
         <v>0.3085106382978723</v>
@@ -4099,10 +4087,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>1529</v>
+        <v>101</v>
       </c>
       <c r="B334" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C334" t="n">
         <v>0.3085106382978723</v>
@@ -4110,10 +4098,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>1502</v>
+        <v>1403</v>
       </c>
       <c r="B335" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C335" t="n">
         <v>0.3085106382978723</v>
@@ -4121,10 +4109,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>1437</v>
+        <v>1966</v>
       </c>
       <c r="B336" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C336" t="n">
         <v>0.3085106382978723</v>
@@ -4132,7 +4120,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>101</v>
+        <v>1907</v>
       </c>
       <c r="B337" t="n">
         <v>2</v>
@@ -4143,10 +4131,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>1388</v>
+        <v>1581</v>
       </c>
       <c r="B338" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C338" t="n">
         <v>0.3085106382978723</v>
@@ -4154,7 +4142,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>1581</v>
+        <v>1588</v>
       </c>
       <c r="B339" t="n">
         <v>2</v>
@@ -4165,10 +4153,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>1588</v>
+        <v>1437</v>
       </c>
       <c r="B340" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C340" t="n">
         <v>0.3085106382978723</v>
@@ -4176,10 +4164,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>1403</v>
+        <v>1502</v>
       </c>
       <c r="B341" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C341" t="n">
         <v>0.3085106382978723</v>
@@ -4187,10 +4175,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="B342" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C342" t="n">
         <v>0.3085106382978723</v>
@@ -4198,10 +4186,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>1532</v>
+        <v>1317</v>
       </c>
       <c r="B343" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C343" t="n">
         <v>0.3085106382978723</v>
@@ -4209,10 +4197,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>1317</v>
+        <v>1536</v>
       </c>
       <c r="B344" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C344" t="n">
         <v>0.3085106382978723</v>
@@ -4220,10 +4208,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>1907</v>
+        <v>1529</v>
       </c>
       <c r="B345" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C345" t="n">
         <v>0.3085106382978723</v>
@@ -4231,10 +4219,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>1966</v>
+        <v>1520</v>
       </c>
       <c r="B346" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C346" t="n">
         <v>0.3085106382978723</v>
@@ -4242,7 +4230,7 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>1536</v>
+        <v>1532</v>
       </c>
       <c r="B347" t="n">
         <v>4</v>
@@ -4264,10 +4252,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>1348</v>
+        <v>1491</v>
       </c>
       <c r="B349" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C349" t="n">
         <v>0.3085106382978723</v>
@@ -4275,10 +4263,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>1491</v>
+        <v>1348</v>
       </c>
       <c r="B350" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C350" t="n">
         <v>0.3085106382978723</v>
@@ -4429,7 +4417,7 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>1258</v>
+        <v>1268</v>
       </c>
       <c r="B364" t="n">
         <v>22</v>
@@ -4440,7 +4428,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>1268</v>
+        <v>1258</v>
       </c>
       <c r="B365" t="n">
         <v>22</v>
@@ -4473,10 +4461,10 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>1133</v>
+        <v>1474</v>
       </c>
       <c r="B368" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C368" t="n">
         <v>0.302127659574468</v>
@@ -4484,10 +4472,10 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>1124</v>
+        <v>1133</v>
       </c>
       <c r="B369" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C369" t="n">
         <v>0.302127659574468</v>
@@ -4495,10 +4483,10 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>1474</v>
+        <v>1124</v>
       </c>
       <c r="B370" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C370" t="n">
         <v>0.302127659574468</v>
@@ -4528,7 +4516,7 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>1449</v>
+        <v>1300</v>
       </c>
       <c r="B373" t="n">
         <v>8</v>
@@ -4539,7 +4527,7 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>1440</v>
+        <v>1449</v>
       </c>
       <c r="B374" t="n">
         <v>8</v>
@@ -4550,7 +4538,7 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>1300</v>
+        <v>1440</v>
       </c>
       <c r="B375" t="n">
         <v>8</v>
@@ -4583,10 +4571,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>1240</v>
+        <v>1350</v>
       </c>
       <c r="B378" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C378" t="n">
         <v>0.2998065764023211</v>
@@ -4594,10 +4582,10 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>1350</v>
+        <v>1240</v>
       </c>
       <c r="B379" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C379" t="n">
         <v>0.2998065764023211</v>
@@ -4638,7 +4626,7 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>1482</v>
+        <v>1942</v>
       </c>
       <c r="B383" t="n">
         <v>3</v>
@@ -4649,7 +4637,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>1942</v>
+        <v>1482</v>
       </c>
       <c r="B384" t="n">
         <v>3</v>
@@ -4660,10 +4648,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>104</v>
+        <v>1183</v>
       </c>
       <c r="B385" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C385" t="n">
         <v>0.2978723404255319</v>
@@ -4682,10 +4670,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>1183</v>
+        <v>1462</v>
       </c>
       <c r="B387" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C387" t="n">
         <v>0.2978723404255319</v>
@@ -4693,7 +4681,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>1462</v>
+        <v>104</v>
       </c>
       <c r="B388" t="n">
         <v>3</v>
@@ -4704,7 +4692,7 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>1266</v>
+        <v>1119</v>
       </c>
       <c r="B389" t="n">
         <v>15</v>
@@ -4715,7 +4703,7 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>1119</v>
+        <v>1266</v>
       </c>
       <c r="B390" t="n">
         <v>15</v>
@@ -4781,7 +4769,7 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>1136</v>
+        <v>1396</v>
       </c>
       <c r="B396" t="n">
         <v>10</v>
@@ -4792,7 +4780,7 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>1396</v>
+        <v>1136</v>
       </c>
       <c r="B397" t="n">
         <v>10</v>
@@ -4825,10 +4813,10 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>1451</v>
+        <v>1307</v>
       </c>
       <c r="B400" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C400" t="n">
         <v>0.2948328267477203</v>
@@ -4836,10 +4824,10 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>1307</v>
+        <v>1451</v>
       </c>
       <c r="B401" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C401" t="n">
         <v>0.2948328267477203</v>
@@ -4957,7 +4945,7 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>1280</v>
+        <v>1259</v>
       </c>
       <c r="B412" t="n">
         <v>22</v>
@@ -4968,7 +4956,7 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>1259</v>
+        <v>1280</v>
       </c>
       <c r="B413" t="n">
         <v>22</v>
@@ -4979,7 +4967,7 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="B414" t="n">
         <v>9</v>
@@ -5001,7 +4989,7 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="B416" t="n">
         <v>9</v>
@@ -5034,10 +5022,10 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>1277</v>
+        <v>1122</v>
       </c>
       <c r="B419" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C419" t="n">
         <v>0.2893617021276595</v>
@@ -5045,10 +5033,10 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>1122</v>
+        <v>1530</v>
       </c>
       <c r="B420" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C420" t="n">
         <v>0.2893617021276595</v>
@@ -5056,7 +5044,7 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>1530</v>
+        <v>1467</v>
       </c>
       <c r="B421" t="n">
         <v>5</v>
@@ -5067,7 +5055,7 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>1214</v>
+        <v>1277</v>
       </c>
       <c r="B422" t="n">
         <v>20</v>
@@ -5078,10 +5066,10 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>1467</v>
+        <v>1214</v>
       </c>
       <c r="B423" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C423" t="n">
         <v>0.2893617021276595</v>
@@ -5188,7 +5176,7 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>1353</v>
+        <v>1296</v>
       </c>
       <c r="B433" t="n">
         <v>13</v>
@@ -5199,7 +5187,7 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>1296</v>
+        <v>1353</v>
       </c>
       <c r="B434" t="n">
         <v>13</v>
@@ -5452,10 +5440,10 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>1564</v>
+        <v>1742</v>
       </c>
       <c r="B457" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C457" t="n">
         <v>0.2765957446808511</v>
@@ -5463,10 +5451,10 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>5449</v>
+        <v>102</v>
       </c>
       <c r="B458" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C458" t="n">
         <v>0.2765957446808511</v>
@@ -5474,10 +5462,10 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B459" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C459" t="n">
         <v>0.2765957446808511</v>
@@ -5485,10 +5473,10 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>5443</v>
+        <v>1929</v>
       </c>
       <c r="B460" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C460" t="n">
         <v>0.2765957446808511</v>
@@ -5496,10 +5484,10 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>1574</v>
+        <v>1291</v>
       </c>
       <c r="B461" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C461" t="n">
         <v>0.2765957446808511</v>
@@ -5507,7 +5495,7 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>5444</v>
+        <v>1926</v>
       </c>
       <c r="B462" t="n">
         <v>1</v>
@@ -5518,10 +5506,10 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>1546</v>
+        <v>1961</v>
       </c>
       <c r="B463" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C463" t="n">
         <v>0.2765957446808511</v>
@@ -5529,10 +5517,10 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>1547</v>
+        <v>1476</v>
       </c>
       <c r="B464" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C464" t="n">
         <v>0.2765957446808511</v>
@@ -5540,10 +5528,10 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>11994</v>
+        <v>1391</v>
       </c>
       <c r="B465" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C465" t="n">
         <v>0.2765957446808511</v>
@@ -5551,10 +5539,10 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>1927</v>
+        <v>1574</v>
       </c>
       <c r="B466" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C466" t="n">
         <v>0.2765957446808511</v>
@@ -5562,10 +5550,10 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>11995</v>
+        <v>1568</v>
       </c>
       <c r="B467" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C467" t="n">
         <v>0.2765957446808511</v>
@@ -5573,10 +5561,10 @@
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>1549</v>
+        <v>1566</v>
       </c>
       <c r="B468" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C468" t="n">
         <v>0.2765957446808511</v>
@@ -5584,10 +5572,10 @@
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>1568</v>
+        <v>1983</v>
       </c>
       <c r="B469" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C469" t="n">
         <v>0.2765957446808511</v>
@@ -5595,10 +5583,10 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>1552</v>
+        <v>5466</v>
       </c>
       <c r="B470" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C470" t="n">
         <v>0.2765957446808511</v>
@@ -5606,10 +5594,10 @@
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>1566</v>
+        <v>5473</v>
       </c>
       <c r="B471" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C471" t="n">
         <v>0.2765957446808511</v>
@@ -5617,10 +5605,10 @@
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>1929</v>
+        <v>5474</v>
       </c>
       <c r="B472" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C472" t="n">
         <v>0.2765957446808511</v>
@@ -5628,10 +5616,10 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>1555</v>
+        <v>1424</v>
       </c>
       <c r="B473" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C473" t="n">
         <v>0.2765957446808511</v>
@@ -5639,10 +5627,10 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>5259</v>
+        <v>4</v>
       </c>
       <c r="B474" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C474" t="n">
         <v>0.2765957446808511</v>
@@ -5650,7 +5638,7 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>1949</v>
+        <v>11995</v>
       </c>
       <c r="B475" t="n">
         <v>1</v>
@@ -5661,7 +5649,7 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>1742</v>
+        <v>11994</v>
       </c>
       <c r="B476" t="n">
         <v>1</v>
@@ -5672,7 +5660,7 @@
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>5454</v>
+        <v>5455</v>
       </c>
       <c r="B477" t="n">
         <v>1</v>
@@ -5683,7 +5671,7 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>5105</v>
+        <v>5454</v>
       </c>
       <c r="B478" t="n">
         <v>1</v>
@@ -5694,7 +5682,7 @@
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>5455</v>
+        <v>5451</v>
       </c>
       <c r="B479" t="n">
         <v>1</v>
@@ -5705,10 +5693,10 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>5451</v>
+        <v>1285</v>
       </c>
       <c r="B480" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C480" t="n">
         <v>0.2765957446808511</v>
@@ -5716,7 +5704,7 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>5277</v>
+        <v>5105</v>
       </c>
       <c r="B481" t="n">
         <v>1</v>
@@ -5727,7 +5715,7 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>5464</v>
+        <v>4418</v>
       </c>
       <c r="B482" t="n">
         <v>1</v>
@@ -5738,10 +5726,10 @@
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>4418</v>
+        <v>1443</v>
       </c>
       <c r="B483" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C483" t="n">
         <v>0.2765957446808511</v>
@@ -5749,10 +5737,10 @@
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>5466</v>
+        <v>442</v>
       </c>
       <c r="B484" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C484" t="n">
         <v>0.2765957446808511</v>
@@ -5760,7 +5748,7 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>1983</v>
+        <v>1949</v>
       </c>
       <c r="B485" t="n">
         <v>1</v>
@@ -5771,7 +5759,7 @@
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>5473</v>
+        <v>1952</v>
       </c>
       <c r="B486" t="n">
         <v>1</v>
@@ -5782,7 +5770,7 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>5280</v>
+        <v>1955</v>
       </c>
       <c r="B487" t="n">
         <v>1</v>
@@ -5793,10 +5781,10 @@
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>1976</v>
+        <v>1460</v>
       </c>
       <c r="B488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C488" t="n">
         <v>0.2765957446808511</v>
@@ -5804,10 +5792,10 @@
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>1961</v>
+        <v>106</v>
       </c>
       <c r="B489" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C489" t="n">
         <v>0.2765957446808511</v>
@@ -5815,7 +5803,7 @@
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>5474</v>
+        <v>5259</v>
       </c>
       <c r="B490" t="n">
         <v>1</v>
@@ -5826,7 +5814,7 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>1955</v>
+        <v>5449</v>
       </c>
       <c r="B491" t="n">
         <v>1</v>
@@ -5837,10 +5825,10 @@
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>1793</v>
+        <v>5464</v>
       </c>
       <c r="B492" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C492" t="n">
         <v>0.2765957446808511</v>
@@ -5848,10 +5836,10 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>1781</v>
+        <v>1489</v>
       </c>
       <c r="B493" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C493" t="n">
         <v>0.2765957446808511</v>
@@ -5859,7 +5847,7 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>2426</v>
+        <v>1976</v>
       </c>
       <c r="B494" t="n">
         <v>1</v>
@@ -5870,10 +5858,10 @@
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>1767</v>
+        <v>1793</v>
       </c>
       <c r="B495" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C495" t="n">
         <v>0.2765957446808511</v>
@@ -5881,7 +5869,7 @@
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>1763</v>
+        <v>1781</v>
       </c>
       <c r="B496" t="n">
         <v>1</v>
@@ -5892,10 +5880,10 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>1762</v>
+        <v>1118</v>
       </c>
       <c r="B497" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C497" t="n">
         <v>0.2765957446808511</v>
@@ -5903,10 +5891,10 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>1952</v>
+        <v>1375</v>
       </c>
       <c r="B498" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C498" t="n">
         <v>0.2765957446808511</v>
@@ -5914,10 +5902,10 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>4</v>
+        <v>1372</v>
       </c>
       <c r="B499" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C499" t="n">
         <v>0.2765957446808511</v>
@@ -5925,10 +5913,10 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>1391</v>
+        <v>1564</v>
       </c>
       <c r="B500" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C500" t="n">
         <v>0.2765957446808511</v>
@@ -5936,10 +5924,10 @@
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>1118</v>
+        <v>1501</v>
       </c>
       <c r="B501" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C501" t="n">
         <v>0.2765957446808511</v>
@@ -5947,10 +5935,10 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>1501</v>
+        <v>1762</v>
       </c>
       <c r="B502" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C502" t="n">
         <v>0.2765957446808511</v>
@@ -5958,10 +5946,10 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>1489</v>
+        <v>1763</v>
       </c>
       <c r="B503" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C503" t="n">
         <v>0.2765957446808511</v>
@@ -5969,10 +5957,10 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>1274</v>
+        <v>1767</v>
       </c>
       <c r="B504" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C504" t="n">
         <v>0.2765957446808511</v>
@@ -5980,10 +5968,10 @@
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>1285</v>
+        <v>1355</v>
       </c>
       <c r="B505" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C505" t="n">
         <v>0.2765957446808511</v>
@@ -5991,10 +5979,10 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>1291</v>
+        <v>1357</v>
       </c>
       <c r="B506" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C506" t="n">
         <v>0.2765957446808511</v>
@@ -6002,10 +5990,10 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>1476</v>
+        <v>5280</v>
       </c>
       <c r="B507" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C507" t="n">
         <v>0.2765957446808511</v>
@@ -6013,10 +6001,10 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>1460</v>
+        <v>5277</v>
       </c>
       <c r="B508" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C508" t="n">
         <v>0.2765957446808511</v>
@@ -6024,10 +6012,10 @@
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>1443</v>
+        <v>1546</v>
       </c>
       <c r="B509" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C509" t="n">
         <v>0.2765957446808511</v>
@@ -6035,10 +6023,10 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>1514</v>
+        <v>2426</v>
       </c>
       <c r="B510" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C510" t="n">
         <v>0.2765957446808511</v>
@@ -6046,10 +6034,10 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>1355</v>
+        <v>1514</v>
       </c>
       <c r="B511" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C511" t="n">
         <v>0.2765957446808511</v>
@@ -6057,10 +6045,10 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>1424</v>
+        <v>1274</v>
       </c>
       <c r="B512" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C512" t="n">
         <v>0.2765957446808511</v>
@@ -6068,10 +6056,10 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>442</v>
+        <v>1549</v>
       </c>
       <c r="B513" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C513" t="n">
         <v>0.2765957446808511</v>
@@ -6079,10 +6067,10 @@
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>1372</v>
+        <v>1547</v>
       </c>
       <c r="B514" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C514" t="n">
         <v>0.2765957446808511</v>
@@ -6090,10 +6078,10 @@
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>102</v>
+        <v>1555</v>
       </c>
       <c r="B515" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C515" t="n">
         <v>0.2765957446808511</v>
@@ -6101,10 +6089,10 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>106</v>
+        <v>1552</v>
       </c>
       <c r="B516" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C516" t="n">
         <v>0.2765957446808511</v>
@@ -6112,7 +6100,7 @@
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>120</v>
+        <v>435</v>
       </c>
       <c r="B517" t="n">
         <v>1</v>
@@ -6123,10 +6111,10 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>1375</v>
+        <v>120</v>
       </c>
       <c r="B518" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C518" t="n">
         <v>0.2765957446808511</v>
@@ -6134,7 +6122,7 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>435</v>
+        <v>5443</v>
       </c>
       <c r="B519" t="n">
         <v>1</v>
@@ -6145,10 +6133,10 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>1357</v>
+        <v>5444</v>
       </c>
       <c r="B520" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C520" t="n">
         <v>0.2765957446808511</v>
@@ -6156,10 +6144,10 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>1416</v>
+        <v>1545</v>
       </c>
       <c r="B521" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C521" t="n">
         <v>0.276595744680851</v>
@@ -6167,10 +6155,10 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>1545</v>
+        <v>1524</v>
       </c>
       <c r="B522" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C522" t="n">
         <v>0.276595744680851</v>
@@ -6178,10 +6166,10 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>1428</v>
+        <v>1272</v>
       </c>
       <c r="B523" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C523" t="n">
         <v>0.276595744680851</v>
@@ -6189,10 +6177,10 @@
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>1283</v>
+        <v>1428</v>
       </c>
       <c r="B524" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C524" t="n">
         <v>0.276595744680851</v>
@@ -6200,10 +6188,10 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>1272</v>
+        <v>1283</v>
       </c>
       <c r="B525" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C525" t="n">
         <v>0.276595744680851</v>
@@ -6211,10 +6199,10 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>1524</v>
+        <v>1416</v>
       </c>
       <c r="B526" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C526" t="n">
         <v>0.276595744680851</v>
@@ -6222,10 +6210,10 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>1412</v>
+        <v>1288</v>
       </c>
       <c r="B527" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C527" t="n">
         <v>0.276595744680851</v>
@@ -6233,10 +6221,10 @@
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>1176</v>
+        <v>1516</v>
       </c>
       <c r="B528" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C528" t="n">
         <v>0.276595744680851</v>
@@ -6244,10 +6232,10 @@
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>1288</v>
+        <v>1412</v>
       </c>
       <c r="B529" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C529" t="n">
         <v>0.276595744680851</v>
@@ -6255,10 +6243,10 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>1344</v>
+        <v>1176</v>
       </c>
       <c r="B530" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C530" t="n">
         <v>0.276595744680851</v>
@@ -6266,10 +6254,10 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>1210</v>
+        <v>1344</v>
       </c>
       <c r="B531" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C531" t="n">
         <v>0.276595744680851</v>
@@ -6277,10 +6265,10 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>1516</v>
+        <v>1210</v>
       </c>
       <c r="B532" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C532" t="n">
         <v>0.276595744680851</v>
@@ -6365,7 +6353,7 @@
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>1207</v>
+        <v>1260</v>
       </c>
       <c r="B540" t="n">
         <v>15</v>
@@ -6376,7 +6364,7 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>1260</v>
+        <v>1207</v>
       </c>
       <c r="B541" t="n">
         <v>15</v>
@@ -6486,7 +6474,7 @@
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>1395</v>
+        <v>1387</v>
       </c>
       <c r="B551" t="n">
         <v>9</v>
@@ -6497,7 +6485,7 @@
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>1387</v>
+        <v>1395</v>
       </c>
       <c r="B552" t="n">
         <v>9</v>
@@ -6519,7 +6507,7 @@
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>1409</v>
+        <v>1381</v>
       </c>
       <c r="B554" t="n">
         <v>8</v>
@@ -6530,7 +6518,7 @@
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>1381</v>
+        <v>1435</v>
       </c>
       <c r="B555" t="n">
         <v>8</v>
@@ -6541,7 +6529,7 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>1435</v>
+        <v>1409</v>
       </c>
       <c r="B556" t="n">
         <v>8</v>
@@ -6618,10 +6606,10 @@
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>1352</v>
+        <v>1515</v>
       </c>
       <c r="B563" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C563" t="n">
         <v>0.2659574468085106</v>
@@ -6629,10 +6617,10 @@
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>1515</v>
+        <v>1352</v>
       </c>
       <c r="B564" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C564" t="n">
         <v>0.2659574468085106</v>
@@ -6640,10 +6628,10 @@
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>1211</v>
+        <v>1531</v>
       </c>
       <c r="B565" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C565" t="n">
         <v>0.2659574468085106</v>
@@ -6651,10 +6639,10 @@
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>1531</v>
+        <v>1211</v>
       </c>
       <c r="B566" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C566" t="n">
         <v>0.2659574468085106</v>
@@ -6783,7 +6771,7 @@
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>1330</v>
+        <v>1250</v>
       </c>
       <c r="B578" t="n">
         <v>13</v>
@@ -6805,7 +6793,7 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>1250</v>
+        <v>1330</v>
       </c>
       <c r="B580" t="n">
         <v>13</v>
@@ -6827,10 +6815,10 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>1319</v>
+        <v>1201</v>
       </c>
       <c r="B582" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C582" t="n">
         <v>0.2606382978723404</v>
@@ -6838,10 +6826,10 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>1201</v>
+        <v>1319</v>
       </c>
       <c r="B583" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C583" t="n">
         <v>0.2606382978723404</v>
@@ -6915,7 +6903,7 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>1512</v>
+        <v>1548</v>
       </c>
       <c r="B590" t="n">
         <v>3</v>
@@ -6926,7 +6914,7 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>1548</v>
+        <v>1512</v>
       </c>
       <c r="B591" t="n">
         <v>3</v>
@@ -6937,10 +6925,10 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>1528</v>
+        <v>1834</v>
       </c>
       <c r="B592" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C592" t="n">
         <v>0.2553191489361702</v>
@@ -6959,10 +6947,10 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>1834</v>
+        <v>1209</v>
       </c>
       <c r="B594" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C594" t="n">
         <v>0.2553191489361702</v>
@@ -6970,10 +6958,10 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>1561</v>
+        <v>1310</v>
       </c>
       <c r="B595" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C595" t="n">
         <v>0.2553191489361702</v>
@@ -6981,10 +6969,10 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>1422</v>
+        <v>1650</v>
       </c>
       <c r="B596" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C596" t="n">
         <v>0.2553191489361702</v>
@@ -6992,10 +6980,10 @@
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>1551</v>
+        <v>1408</v>
       </c>
       <c r="B597" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C597" t="n">
         <v>0.2553191489361702</v>
@@ -7014,10 +7002,10 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>1408</v>
+        <v>1422</v>
       </c>
       <c r="B599" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C599" t="n">
         <v>0.2553191489361702</v>
@@ -7025,10 +7013,10 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>1209</v>
+        <v>1528</v>
       </c>
       <c r="B600" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C600" t="n">
         <v>0.2553191489361702</v>
@@ -7036,7 +7024,7 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>1511</v>
+        <v>1551</v>
       </c>
       <c r="B601" t="n">
         <v>3</v>
@@ -7047,10 +7035,10 @@
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>1310</v>
+        <v>1561</v>
       </c>
       <c r="B602" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C602" t="n">
         <v>0.2553191489361702</v>
@@ -7058,7 +7046,7 @@
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>1650</v>
+        <v>1511</v>
       </c>
       <c r="B603" t="n">
         <v>3</v>
@@ -7190,7 +7178,7 @@
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>1425</v>
+        <v>1374</v>
       </c>
       <c r="B615" t="n">
         <v>9</v>
@@ -7201,7 +7189,7 @@
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>1374</v>
+        <v>1425</v>
       </c>
       <c r="B616" t="n">
         <v>9</v>
@@ -7212,10 +7200,10 @@
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>1278</v>
+        <v>1376</v>
       </c>
       <c r="B617" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C617" t="n">
         <v>0.2482269503546099</v>
@@ -7223,10 +7211,10 @@
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>1376</v>
+        <v>1278</v>
       </c>
       <c r="B618" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C618" t="n">
         <v>0.2482269503546099</v>
@@ -7267,10 +7255,10 @@
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>1541</v>
+        <v>1356</v>
       </c>
       <c r="B622" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C622" t="n">
         <v>0.2446808510638298</v>
@@ -7278,7 +7266,7 @@
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>1684</v>
+        <v>1648</v>
       </c>
       <c r="B623" t="n">
         <v>2</v>
@@ -7289,10 +7277,10 @@
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>1363</v>
+        <v>1308</v>
       </c>
       <c r="B624" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C624" t="n">
         <v>0.2446808510638298</v>
@@ -7300,10 +7288,10 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>1361</v>
+        <v>1480</v>
       </c>
       <c r="B625" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C625" t="n">
         <v>0.2446808510638298</v>
@@ -7311,7 +7299,7 @@
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>1473</v>
+        <v>1563</v>
       </c>
       <c r="B626" t="n">
         <v>2</v>
@@ -7322,10 +7310,10 @@
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>1360</v>
+        <v>1541</v>
       </c>
       <c r="B627" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C627" t="n">
         <v>0.2446808510638298</v>
@@ -7333,10 +7321,10 @@
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>1468</v>
+        <v>1521</v>
       </c>
       <c r="B628" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C628" t="n">
         <v>0.2446808510638298</v>
@@ -7344,10 +7332,10 @@
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>1356</v>
+        <v>1468</v>
       </c>
       <c r="B629" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C629" t="n">
         <v>0.2446808510638298</v>
@@ -7355,7 +7343,7 @@
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>1648</v>
+        <v>1473</v>
       </c>
       <c r="B630" t="n">
         <v>2</v>
@@ -7366,10 +7354,10 @@
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>1126</v>
+        <v>1486</v>
       </c>
       <c r="B631" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C631" t="n">
         <v>0.2446808510638298</v>
@@ -7377,10 +7365,10 @@
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>1486</v>
+        <v>1962</v>
       </c>
       <c r="B632" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C632" t="n">
         <v>0.2446808510638298</v>
@@ -7388,10 +7376,10 @@
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>1521</v>
+        <v>1360</v>
       </c>
       <c r="B633" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C633" t="n">
         <v>0.2446808510638298</v>
@@ -7399,10 +7387,10 @@
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>1946</v>
+        <v>1414</v>
       </c>
       <c r="B634" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C634" t="n">
         <v>0.2446808510638298</v>
@@ -7410,10 +7398,10 @@
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>1953</v>
+        <v>1126</v>
       </c>
       <c r="B635" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C635" t="n">
         <v>0.2446808510638298</v>
@@ -7421,7 +7409,7 @@
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>1563</v>
+        <v>1946</v>
       </c>
       <c r="B636" t="n">
         <v>2</v>
@@ -7432,10 +7420,10 @@
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>1480</v>
+        <v>1459</v>
       </c>
       <c r="B637" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C637" t="n">
         <v>0.2446808510638298</v>
@@ -7443,10 +7431,10 @@
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>1414</v>
+        <v>1953</v>
       </c>
       <c r="B638" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C638" t="n">
         <v>0.2446808510638298</v>
@@ -7454,10 +7442,10 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>1962</v>
+        <v>1363</v>
       </c>
       <c r="B639" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C639" t="n">
         <v>0.2446808510638298</v>
@@ -7465,10 +7453,10 @@
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>1459</v>
+        <v>1361</v>
       </c>
       <c r="B640" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C640" t="n">
         <v>0.2446808510638298</v>
@@ -7476,10 +7464,10 @@
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>1308</v>
+        <v>1684</v>
       </c>
       <c r="B641" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C641" t="n">
         <v>0.2446808510638298</v>
@@ -7520,7 +7508,7 @@
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>1369</v>
+        <v>1311</v>
       </c>
       <c r="B645" t="n">
         <v>9</v>
@@ -7531,7 +7519,7 @@
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>1311</v>
+        <v>1369</v>
       </c>
       <c r="B646" t="n">
         <v>9</v>
@@ -7575,7 +7563,7 @@
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>1534</v>
+        <v>1447</v>
       </c>
       <c r="B650" t="n">
         <v>5</v>
@@ -7586,10 +7574,10 @@
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>1417</v>
+        <v>1405</v>
       </c>
       <c r="B651" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C651" t="n">
         <v>0.2382978723404255</v>
@@ -7597,10 +7585,10 @@
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>1494</v>
+        <v>1417</v>
       </c>
       <c r="B652" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C652" t="n">
         <v>0.2382978723404255</v>
@@ -7608,7 +7596,7 @@
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>1405</v>
+        <v>1494</v>
       </c>
       <c r="B653" t="n">
         <v>5</v>
@@ -7630,7 +7618,7 @@
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>1464</v>
+        <v>1534</v>
       </c>
       <c r="B655" t="n">
         <v>5</v>
@@ -7641,7 +7629,7 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>1447</v>
+        <v>1464</v>
       </c>
       <c r="B656" t="n">
         <v>5</v>
@@ -7674,7 +7662,7 @@
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="B659" t="n">
         <v>8</v>
@@ -7685,7 +7673,7 @@
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="B660" t="n">
         <v>8</v>
@@ -7751,7 +7739,7 @@
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>1526</v>
+        <v>1557</v>
       </c>
       <c r="B666" t="n">
         <v>3</v>
@@ -7762,10 +7750,10 @@
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>1557</v>
+        <v>1301</v>
       </c>
       <c r="B667" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C667" t="n">
         <v>0.2340425531914894</v>
@@ -7773,10 +7761,10 @@
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>1301</v>
+        <v>1507</v>
       </c>
       <c r="B668" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C668" t="n">
         <v>0.2340425531914894</v>
@@ -7795,10 +7783,10 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>1389</v>
+        <v>1526</v>
       </c>
       <c r="B670" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C670" t="n">
         <v>0.2340425531914894</v>
@@ -7806,10 +7794,10 @@
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>1427</v>
+        <v>1479</v>
       </c>
       <c r="B671" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C671" t="n">
         <v>0.2340425531914894</v>
@@ -7817,10 +7805,10 @@
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>1479</v>
+        <v>1427</v>
       </c>
       <c r="B672" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C672" t="n">
         <v>0.2340425531914894</v>
@@ -7828,10 +7816,10 @@
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>1507</v>
+        <v>1380</v>
       </c>
       <c r="B673" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C673" t="n">
         <v>0.2340425531914894</v>
@@ -7839,10 +7827,10 @@
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>1380</v>
+        <v>1389</v>
       </c>
       <c r="B674" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C674" t="n">
         <v>0.2340425531914894</v>
@@ -7949,10 +7937,10 @@
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>1431</v>
+        <v>1595</v>
       </c>
       <c r="B684" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C684" t="n">
         <v>0.2287234042553191</v>
@@ -7971,7 +7959,7 @@
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>1595</v>
+        <v>1496</v>
       </c>
       <c r="B686" t="n">
         <v>4</v>
@@ -7982,10 +7970,10 @@
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>1496</v>
+        <v>1431</v>
       </c>
       <c r="B687" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C687" t="n">
         <v>0.2287234042553191</v>
@@ -8092,7 +8080,7 @@
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>4400</v>
+        <v>175</v>
       </c>
       <c r="B697" t="n">
         <v>1</v>
@@ -8103,7 +8091,7 @@
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>2705</v>
+        <v>192</v>
       </c>
       <c r="B698" t="n">
         <v>1</v>
@@ -8114,10 +8102,10 @@
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>1497</v>
+        <v>1313</v>
       </c>
       <c r="B699" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C699" t="n">
         <v>0.2127659574468085</v>
@@ -8125,10 +8113,10 @@
     </row>
     <row r="700">
       <c r="A700" t="n">
-        <v>1601</v>
+        <v>75</v>
       </c>
       <c r="B700" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C700" t="n">
         <v>0.2127659574468085</v>
@@ -8136,10 +8124,10 @@
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>1481</v>
+        <v>67</v>
       </c>
       <c r="B701" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C701" t="n">
         <v>0.2127659574468085</v>
@@ -8147,7 +8135,7 @@
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>2739</v>
+        <v>58</v>
       </c>
       <c r="B702" t="n">
         <v>1</v>
@@ -8158,10 +8146,10 @@
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>1603</v>
+        <v>1708</v>
       </c>
       <c r="B703" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C703" t="n">
         <v>0.2127659574468085</v>
@@ -8169,7 +8157,7 @@
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>2729</v>
+        <v>1758</v>
       </c>
       <c r="B704" t="n">
         <v>1</v>
@@ -8180,10 +8168,10 @@
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>1605</v>
+        <v>1759</v>
       </c>
       <c r="B705" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C705" t="n">
         <v>0.2127659574468085</v>
@@ -8191,7 +8179,7 @@
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>4387</v>
+        <v>1789</v>
       </c>
       <c r="B706" t="n">
         <v>1</v>
@@ -8202,7 +8190,7 @@
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>2708</v>
+        <v>1796</v>
       </c>
       <c r="B707" t="n">
         <v>1</v>
@@ -8213,7 +8201,7 @@
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>4390</v>
+        <v>1797</v>
       </c>
       <c r="B708" t="n">
         <v>1</v>
@@ -8224,7 +8212,7 @@
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>2703</v>
+        <v>1801</v>
       </c>
       <c r="B709" t="n">
         <v>1</v>
@@ -8235,7 +8223,7 @@
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>1584</v>
+        <v>1802</v>
       </c>
       <c r="B710" t="n">
         <v>1</v>
@@ -8246,7 +8234,7 @@
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>4402</v>
+        <v>1803</v>
       </c>
       <c r="B711" t="n">
         <v>1</v>
@@ -8257,10 +8245,10 @@
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>4382</v>
+        <v>1804</v>
       </c>
       <c r="B712" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C712" t="n">
         <v>0.2127659574468085</v>
@@ -8268,7 +8256,7 @@
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>4396</v>
+        <v>1806</v>
       </c>
       <c r="B713" t="n">
         <v>1</v>
@@ -8279,7 +8267,7 @@
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>2701</v>
+        <v>1807</v>
       </c>
       <c r="B714" t="n">
         <v>1</v>
@@ -8290,7 +8278,7 @@
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>2688</v>
+        <v>1808</v>
       </c>
       <c r="B715" t="n">
         <v>1</v>
@@ -8301,7 +8289,7 @@
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>4397</v>
+        <v>5243</v>
       </c>
       <c r="B716" t="n">
         <v>1</v>
@@ -8312,10 +8300,10 @@
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>1607</v>
+        <v>5275</v>
       </c>
       <c r="B717" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C717" t="n">
         <v>0.2127659574468085</v>
@@ -8323,7 +8311,7 @@
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>2694</v>
+        <v>1815</v>
       </c>
       <c r="B718" t="n">
         <v>1</v>
@@ -8334,7 +8322,7 @@
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>4399</v>
+        <v>1817</v>
       </c>
       <c r="B719" t="n">
         <v>1</v>
@@ -8345,10 +8333,10 @@
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>2690</v>
+        <v>1818</v>
       </c>
       <c r="B720" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C720" t="n">
         <v>0.2127659574468085</v>
@@ -8356,7 +8344,7 @@
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>3806</v>
+        <v>1819</v>
       </c>
       <c r="B721" t="n">
         <v>1</v>
@@ -8367,7 +8355,7 @@
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>4379</v>
+        <v>1822</v>
       </c>
       <c r="B722" t="n">
         <v>1</v>
@@ -8378,7 +8366,7 @@
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>3809</v>
+        <v>1823</v>
       </c>
       <c r="B723" t="n">
         <v>1</v>
@@ -8389,7 +8377,7 @@
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>3792</v>
+        <v>1824</v>
       </c>
       <c r="B724" t="n">
         <v>1</v>
@@ -8400,7 +8388,7 @@
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>3810</v>
+        <v>1825</v>
       </c>
       <c r="B725" t="n">
         <v>1</v>
@@ -8411,10 +8399,10 @@
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>1487</v>
+        <v>1828</v>
       </c>
       <c r="B726" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C726" t="n">
         <v>0.2127659574468085</v>
@@ -8422,7 +8410,7 @@
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>3812</v>
+        <v>1829</v>
       </c>
       <c r="B727" t="n">
         <v>1</v>
@@ -8433,7 +8421,7 @@
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>3821</v>
+        <v>1832</v>
       </c>
       <c r="B728" t="n">
         <v>1</v>
@@ -8444,10 +8432,10 @@
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>1592</v>
+        <v>1833</v>
       </c>
       <c r="B729" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C729" t="n">
         <v>0.2127659574468085</v>
@@ -8455,7 +8443,7 @@
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>3829</v>
+        <v>1746</v>
       </c>
       <c r="B730" t="n">
         <v>1</v>
@@ -8466,10 +8454,10 @@
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>1498</v>
+        <v>1748</v>
       </c>
       <c r="B731" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C731" t="n">
         <v>0.2127659574468085</v>
@@ -8477,7 +8465,7 @@
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>3834</v>
+        <v>1753</v>
       </c>
       <c r="B732" t="n">
         <v>1</v>
@@ -8488,7 +8476,7 @@
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>3803</v>
+        <v>1755</v>
       </c>
       <c r="B733" t="n">
         <v>1</v>
@@ -8499,7 +8487,7 @@
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>3797</v>
+        <v>1658</v>
       </c>
       <c r="B734" t="n">
         <v>1</v>
@@ -8510,7 +8498,7 @@
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>4102</v>
+        <v>1661</v>
       </c>
       <c r="B735" t="n">
         <v>1</v>
@@ -8521,10 +8509,10 @@
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>4353</v>
+        <v>1663</v>
       </c>
       <c r="B736" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C736" t="n">
         <v>0.2127659574468085</v>
@@ -8532,7 +8520,7 @@
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>4376</v>
+        <v>1665</v>
       </c>
       <c r="B737" t="n">
         <v>1</v>
@@ -8543,7 +8531,7 @@
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>3787</v>
+        <v>1670</v>
       </c>
       <c r="B738" t="n">
         <v>1</v>
@@ -8554,10 +8542,10 @@
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>4359</v>
+        <v>1671</v>
       </c>
       <c r="B739" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C739" t="n">
         <v>0.2127659574468085</v>
@@ -8565,7 +8553,7 @@
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>3785</v>
+        <v>1675</v>
       </c>
       <c r="B740" t="n">
         <v>1</v>
@@ -8576,7 +8564,7 @@
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>4360</v>
+        <v>1676</v>
       </c>
       <c r="B741" t="n">
         <v>1</v>
@@ -8587,7 +8575,7 @@
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>1596</v>
+        <v>1679</v>
       </c>
       <c r="B742" t="n">
         <v>1</v>
@@ -8598,10 +8586,10 @@
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>1484</v>
+        <v>1681</v>
       </c>
       <c r="B743" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C743" t="n">
         <v>0.2127659574468085</v>
@@ -8609,10 +8597,10 @@
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>1598</v>
+        <v>1686</v>
       </c>
       <c r="B744" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C744" t="n">
         <v>0.2127659574468085</v>
@@ -8620,10 +8608,10 @@
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>4362</v>
+        <v>1688</v>
       </c>
       <c r="B745" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C745" t="n">
         <v>0.2127659574468085</v>
@@ -8631,7 +8619,7 @@
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>1599</v>
+        <v>1809</v>
       </c>
       <c r="B746" t="n">
         <v>1</v>
@@ -8642,10 +8630,10 @@
     </row>
     <row r="747">
       <c r="A747" t="n">
-        <v>1483</v>
+        <v>1811</v>
       </c>
       <c r="B747" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C747" t="n">
         <v>0.2127659574468085</v>
@@ -8653,7 +8641,7 @@
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>4374</v>
+        <v>1812</v>
       </c>
       <c r="B748" t="n">
         <v>1</v>
@@ -8664,7 +8652,7 @@
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>3833</v>
+        <v>1813</v>
       </c>
       <c r="B749" t="n">
         <v>1</v>
@@ -8675,7 +8663,7 @@
     </row>
     <row r="750">
       <c r="A750" t="n">
-        <v>5108</v>
+        <v>1842</v>
       </c>
       <c r="B750" t="n">
         <v>1</v>
@@ -8686,10 +8674,10 @@
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>1499</v>
+        <v>1843</v>
       </c>
       <c r="B751" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C751" t="n">
         <v>0.2127659574468085</v>
@@ -8697,7 +8685,7 @@
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>390</v>
+        <v>1845</v>
       </c>
       <c r="B752" t="n">
         <v>1</v>
@@ -8708,7 +8696,7 @@
     </row>
     <row r="753">
       <c r="A753" t="n">
-        <v>175</v>
+        <v>1854</v>
       </c>
       <c r="B753" t="n">
         <v>1</v>
@@ -8719,7 +8707,7 @@
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>192</v>
+        <v>1857</v>
       </c>
       <c r="B754" t="n">
         <v>1</v>
@@ -8730,10 +8718,10 @@
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>197</v>
+        <v>1858</v>
       </c>
       <c r="B755" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C755" t="n">
         <v>0.2127659574468085</v>
@@ -8741,7 +8729,7 @@
     </row>
     <row r="756">
       <c r="A756" t="n">
-        <v>5468</v>
+        <v>1895</v>
       </c>
       <c r="B756" t="n">
         <v>1</v>
@@ -8752,7 +8740,7 @@
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>236</v>
+        <v>1900</v>
       </c>
       <c r="B757" t="n">
         <v>1</v>
@@ -8763,7 +8751,7 @@
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>276</v>
+        <v>1636</v>
       </c>
       <c r="B758" t="n">
         <v>1</v>
@@ -8774,10 +8762,10 @@
     </row>
     <row r="759">
       <c r="A759" t="n">
-        <v>372</v>
+        <v>1637</v>
       </c>
       <c r="B759" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C759" t="n">
         <v>0.2127659574468085</v>
@@ -8785,10 +8773,10 @@
     </row>
     <row r="760">
       <c r="A760" t="n">
-        <v>401</v>
+        <v>1639</v>
       </c>
       <c r="B760" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C760" t="n">
         <v>0.2127659574468085</v>
@@ -8796,10 +8784,10 @@
     </row>
     <row r="761">
       <c r="A761" t="n">
-        <v>4407</v>
+        <v>1647</v>
       </c>
       <c r="B761" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C761" t="n">
         <v>0.2127659574468085</v>
@@ -8807,7 +8795,7 @@
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>419</v>
+        <v>1835</v>
       </c>
       <c r="B762" t="n">
         <v>1</v>
@@ -8818,7 +8806,7 @@
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>438</v>
+        <v>1836</v>
       </c>
       <c r="B763" t="n">
         <v>1</v>
@@ -8829,10 +8817,10 @@
     </row>
     <row r="764">
       <c r="A764" t="n">
-        <v>1527</v>
+        <v>1838</v>
       </c>
       <c r="B764" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C764" t="n">
         <v>0.2127659574468085</v>
@@ -8840,7 +8828,7 @@
     </row>
     <row r="765">
       <c r="A765" t="n">
-        <v>457</v>
+        <v>1841</v>
       </c>
       <c r="B765" t="n">
         <v>1</v>
@@ -8851,7 +8839,7 @@
     </row>
     <row r="766">
       <c r="A766" t="n">
-        <v>5447</v>
+        <v>1909</v>
       </c>
       <c r="B766" t="n">
         <v>1</v>
@@ -8862,7 +8850,7 @@
     </row>
     <row r="767">
       <c r="A767" t="n">
-        <v>5446</v>
+        <v>1912</v>
       </c>
       <c r="B767" t="n">
         <v>1</v>
@@ -8873,7 +8861,7 @@
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>619</v>
+        <v>1913</v>
       </c>
       <c r="B768" t="n">
         <v>1</v>
@@ -8884,10 +8872,10 @@
     </row>
     <row r="769">
       <c r="A769" t="n">
-        <v>139</v>
+        <v>1914</v>
       </c>
       <c r="B769" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C769" t="n">
         <v>0.2127659574468085</v>
@@ -8895,7 +8883,7 @@
     </row>
     <row r="770">
       <c r="A770" t="n">
-        <v>128</v>
+        <v>1916</v>
       </c>
       <c r="B770" t="n">
         <v>1</v>
@@ -8906,7 +8894,7 @@
     </row>
     <row r="771">
       <c r="A771" t="n">
-        <v>5503</v>
+        <v>1918</v>
       </c>
       <c r="B771" t="n">
         <v>1</v>
@@ -8917,7 +8905,7 @@
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>1538</v>
+        <v>1920</v>
       </c>
       <c r="B772" t="n">
         <v>2</v>
@@ -8928,7 +8916,7 @@
     </row>
     <row r="773">
       <c r="A773" t="n">
-        <v>20220</v>
+        <v>1928</v>
       </c>
       <c r="B773" t="n">
         <v>1</v>
@@ -8939,10 +8927,10 @@
     </row>
     <row r="774">
       <c r="A774" t="n">
-        <v>12</v>
+        <v>1605</v>
       </c>
       <c r="B774" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C774" t="n">
         <v>0.2127659574468085</v>
@@ -8950,10 +8938,10 @@
     </row>
     <row r="775">
       <c r="A775" t="n">
-        <v>11999</v>
+        <v>1607</v>
       </c>
       <c r="B775" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C775" t="n">
         <v>0.2127659574468085</v>
@@ -8961,7 +8949,7 @@
     </row>
     <row r="776">
       <c r="A776" t="n">
-        <v>11998</v>
+        <v>1611</v>
       </c>
       <c r="B776" t="n">
         <v>1</v>
@@ -8972,7 +8960,7 @@
     </row>
     <row r="777">
       <c r="A777" t="n">
-        <v>52</v>
+        <v>1613</v>
       </c>
       <c r="B777" t="n">
         <v>1</v>
@@ -8983,7 +8971,7 @@
     </row>
     <row r="778">
       <c r="A778" t="n">
-        <v>11996</v>
+        <v>1653</v>
       </c>
       <c r="B778" t="n">
         <v>1</v>
@@ -8994,7 +8982,7 @@
     </row>
     <row r="779">
       <c r="A779" t="n">
-        <v>58</v>
+        <v>1655</v>
       </c>
       <c r="B779" t="n">
         <v>1</v>
@@ -9005,7 +8993,7 @@
     </row>
     <row r="780">
       <c r="A780" t="n">
-        <v>67</v>
+        <v>1657</v>
       </c>
       <c r="B780" t="n">
         <v>1</v>
@@ -9016,7 +9004,7 @@
     </row>
     <row r="781">
       <c r="A781" t="n">
-        <v>11993</v>
+        <v>1630</v>
       </c>
       <c r="B781" t="n">
         <v>1</v>
@@ -9027,7 +9015,7 @@
     </row>
     <row r="782">
       <c r="A782" t="n">
-        <v>11990</v>
+        <v>1931</v>
       </c>
       <c r="B782" t="n">
         <v>1</v>
@@ -9038,7 +9026,7 @@
     </row>
     <row r="783">
       <c r="A783" t="n">
-        <v>11920</v>
+        <v>1932</v>
       </c>
       <c r="B783" t="n">
         <v>1</v>
@@ -9049,10 +9037,10 @@
     </row>
     <row r="784">
       <c r="A784" t="n">
-        <v>75</v>
+        <v>1933</v>
       </c>
       <c r="B784" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C784" t="n">
         <v>0.2127659574468085</v>
@@ -9060,7 +9048,7 @@
     </row>
     <row r="785">
       <c r="A785" t="n">
-        <v>90</v>
+        <v>1935</v>
       </c>
       <c r="B785" t="n">
         <v>1</v>
@@ -9071,10 +9059,10 @@
     </row>
     <row r="786">
       <c r="A786" t="n">
-        <v>1533</v>
+        <v>1939</v>
       </c>
       <c r="B786" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C786" t="n">
         <v>0.2127659574468085</v>
@@ -9082,7 +9070,7 @@
     </row>
     <row r="787">
       <c r="A787" t="n">
-        <v>1537</v>
+        <v>1941</v>
       </c>
       <c r="B787" t="n">
         <v>2</v>
@@ -9093,7 +9081,7 @@
     </row>
     <row r="788">
       <c r="A788" t="n">
-        <v>860</v>
+        <v>1943</v>
       </c>
       <c r="B788" t="n">
         <v>1</v>
@@ -9104,10 +9092,10 @@
     </row>
     <row r="789">
       <c r="A789" t="n">
-        <v>5442</v>
+        <v>1947</v>
       </c>
       <c r="B789" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C789" t="n">
         <v>0.2127659574468085</v>
@@ -9115,7 +9103,7 @@
     </row>
     <row r="790">
       <c r="A790" t="n">
-        <v>1010</v>
+        <v>1954</v>
       </c>
       <c r="B790" t="n">
         <v>1</v>
@@ -9126,7 +9114,7 @@
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>5282</v>
+        <v>1956</v>
       </c>
       <c r="B791" t="n">
         <v>1</v>
@@ -9137,10 +9125,10 @@
     </row>
     <row r="792">
       <c r="A792" t="n">
-        <v>1560</v>
+        <v>1599</v>
       </c>
       <c r="B792" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C792" t="n">
         <v>0.2127659574468085</v>
@@ -9148,7 +9136,7 @@
     </row>
     <row r="793">
       <c r="A793" t="n">
-        <v>5275</v>
+        <v>1904</v>
       </c>
       <c r="B793" t="n">
         <v>1</v>
@@ -9159,10 +9147,10 @@
     </row>
     <row r="794">
       <c r="A794" t="n">
-        <v>1519</v>
+        <v>1905</v>
       </c>
       <c r="B794" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C794" t="n">
         <v>0.2127659574468085</v>
@@ -9170,10 +9158,10 @@
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>1518</v>
+        <v>1906</v>
       </c>
       <c r="B795" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C795" t="n">
         <v>0.2127659574468085</v>
@@ -9181,10 +9169,10 @@
     </row>
     <row r="796">
       <c r="A796" t="n">
-        <v>1517</v>
+        <v>1908</v>
       </c>
       <c r="B796" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C796" t="n">
         <v>0.2127659574468085</v>
@@ -9192,7 +9180,7 @@
     </row>
     <row r="797">
       <c r="A797" t="n">
-        <v>5243</v>
+        <v>1964</v>
       </c>
       <c r="B797" t="n">
         <v>1</v>
@@ -9203,7 +9191,7 @@
     </row>
     <row r="798">
       <c r="A798" t="n">
-        <v>5242</v>
+        <v>2015</v>
       </c>
       <c r="B798" t="n">
         <v>1</v>
@@ -9214,7 +9202,7 @@
     </row>
     <row r="799">
       <c r="A799" t="n">
-        <v>1513</v>
+        <v>2016</v>
       </c>
       <c r="B799" t="n">
         <v>1</v>
@@ -9225,7 +9213,7 @@
     </row>
     <row r="800">
       <c r="A800" t="n">
-        <v>5169</v>
+        <v>2017</v>
       </c>
       <c r="B800" t="n">
         <v>1</v>
@@ -9236,10 +9224,10 @@
     </row>
     <row r="801">
       <c r="A801" t="n">
-        <v>1510</v>
+        <v>2018</v>
       </c>
       <c r="B801" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C801" t="n">
         <v>0.2127659574468085</v>
@@ -9247,7 +9235,7 @@
     </row>
     <row r="802">
       <c r="A802" t="n">
-        <v>2683</v>
+        <v>2023</v>
       </c>
       <c r="B802" t="n">
         <v>1</v>
@@ -9258,10 +9246,10 @@
     </row>
     <row r="803">
       <c r="A803" t="n">
-        <v>1505</v>
+        <v>2094</v>
       </c>
       <c r="B803" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C803" t="n">
         <v>0.2127659574468085</v>
@@ -9269,7 +9257,7 @@
     </row>
     <row r="804">
       <c r="A804" t="n">
-        <v>4416</v>
+        <v>2097</v>
       </c>
       <c r="B804" t="n">
         <v>1</v>
@@ -9280,7 +9268,7 @@
     </row>
     <row r="805">
       <c r="A805" t="n">
-        <v>4413</v>
+        <v>2099</v>
       </c>
       <c r="B805" t="n">
         <v>1</v>
@@ -9291,10 +9279,10 @@
     </row>
     <row r="806">
       <c r="A806" t="n">
-        <v>1500</v>
+        <v>1584</v>
       </c>
       <c r="B806" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C806" t="n">
         <v>0.2127659574468085</v>
@@ -9302,7 +9290,7 @@
     </row>
     <row r="807">
       <c r="A807" t="n">
-        <v>1559</v>
+        <v>1592</v>
       </c>
       <c r="B807" t="n">
         <v>2</v>
@@ -9313,7 +9301,7 @@
     </row>
     <row r="808">
       <c r="A808" t="n">
-        <v>5284</v>
+        <v>1617</v>
       </c>
       <c r="B808" t="n">
         <v>1</v>
@@ -9324,7 +9312,7 @@
     </row>
     <row r="809">
       <c r="A809" t="n">
-        <v>1069</v>
+        <v>1620</v>
       </c>
       <c r="B809" t="n">
         <v>1</v>
@@ -9335,10 +9323,10 @@
     </row>
     <row r="810">
       <c r="A810" t="n">
-        <v>5285</v>
+        <v>1625</v>
       </c>
       <c r="B810" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C810" t="n">
         <v>0.2127659574468085</v>
@@ -9346,7 +9334,7 @@
     </row>
     <row r="811">
       <c r="A811" t="n">
-        <v>1112</v>
+        <v>1627</v>
       </c>
       <c r="B811" t="n">
         <v>1</v>
@@ -9357,7 +9345,7 @@
     </row>
     <row r="812">
       <c r="A812" t="n">
-        <v>5424</v>
+        <v>2108</v>
       </c>
       <c r="B812" t="n">
         <v>1</v>
@@ -9368,7 +9356,7 @@
     </row>
     <row r="813">
       <c r="A813" t="n">
-        <v>1113</v>
+        <v>2109</v>
       </c>
       <c r="B813" t="n">
         <v>1</v>
@@ -9379,7 +9367,7 @@
     </row>
     <row r="814">
       <c r="A814" t="n">
-        <v>1114</v>
+        <v>2110</v>
       </c>
       <c r="B814" t="n">
         <v>1</v>
@@ -9390,7 +9378,7 @@
     </row>
     <row r="815">
       <c r="A815" t="n">
-        <v>10</v>
+        <v>2112</v>
       </c>
       <c r="B815" t="n">
         <v>1</v>
@@ -9401,7 +9389,7 @@
     </row>
     <row r="816">
       <c r="A816" t="n">
-        <v>5356</v>
+        <v>2118</v>
       </c>
       <c r="B816" t="n">
         <v>1</v>
@@ -9412,10 +9400,10 @@
     </row>
     <row r="817">
       <c r="A817" t="n">
-        <v>1553</v>
+        <v>2120</v>
       </c>
       <c r="B817" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C817" t="n">
         <v>0.2127659574468085</v>
@@ -9423,7 +9411,7 @@
     </row>
     <row r="818">
       <c r="A818" t="n">
-        <v>1554</v>
+        <v>2123</v>
       </c>
       <c r="B818" t="n">
         <v>1</v>
@@ -9434,10 +9422,10 @@
     </row>
     <row r="819">
       <c r="A819" t="n">
-        <v>5317</v>
+        <v>1553</v>
       </c>
       <c r="B819" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C819" t="n">
         <v>0.2127659574468085</v>
@@ -9445,10 +9433,10 @@
     </row>
     <row r="820">
       <c r="A820" t="n">
-        <v>1522</v>
+        <v>1554</v>
       </c>
       <c r="B820" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C820" t="n">
         <v>0.2127659574468085</v>
@@ -9467,10 +9455,10 @@
     </row>
     <row r="822">
       <c r="A822" t="n">
-        <v>5289</v>
+        <v>1559</v>
       </c>
       <c r="B822" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C822" t="n">
         <v>0.2127659574468085</v>
@@ -9478,10 +9466,10 @@
     </row>
     <row r="823">
       <c r="A823" t="n">
-        <v>5288</v>
+        <v>1560</v>
       </c>
       <c r="B823" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C823" t="n">
         <v>0.2127659574468085</v>
@@ -9489,10 +9477,10 @@
     </row>
     <row r="824">
       <c r="A824" t="n">
-        <v>5287</v>
+        <v>1601</v>
       </c>
       <c r="B824" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C824" t="n">
         <v>0.2127659574468085</v>
@@ -9500,10 +9488,10 @@
     </row>
     <row r="825">
       <c r="A825" t="n">
-        <v>5286</v>
+        <v>1603</v>
       </c>
       <c r="B825" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C825" t="n">
         <v>0.2127659574468085</v>
@@ -9511,7 +9499,7 @@
     </row>
     <row r="826">
       <c r="A826" t="n">
-        <v>2686</v>
+        <v>1959</v>
       </c>
       <c r="B826" t="n">
         <v>1</v>
@@ -9522,7 +9510,7 @@
     </row>
     <row r="827">
       <c r="A827" t="n">
-        <v>2657</v>
+        <v>1960</v>
       </c>
       <c r="B827" t="n">
         <v>1</v>
@@ -9533,10 +9521,10 @@
     </row>
     <row r="828">
       <c r="A828" t="n">
-        <v>2681</v>
+        <v>1537</v>
       </c>
       <c r="B828" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C828" t="n">
         <v>0.2127659574468085</v>
@@ -9544,10 +9532,10 @@
     </row>
     <row r="829">
       <c r="A829" t="n">
-        <v>1908</v>
+        <v>1538</v>
       </c>
       <c r="B829" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C829" t="n">
         <v>0.2127659574468085</v>
@@ -9555,7 +9543,7 @@
     </row>
     <row r="830">
       <c r="A830" t="n">
-        <v>1829</v>
+        <v>2124</v>
       </c>
       <c r="B830" t="n">
         <v>1</v>
@@ -9566,7 +9554,7 @@
     </row>
     <row r="831">
       <c r="A831" t="n">
-        <v>1828</v>
+        <v>2126</v>
       </c>
       <c r="B831" t="n">
         <v>1</v>
@@ -9577,7 +9565,7 @@
     </row>
     <row r="832">
       <c r="A832" t="n">
-        <v>1825</v>
+        <v>2129</v>
       </c>
       <c r="B832" t="n">
         <v>1</v>
@@ -9588,7 +9576,7 @@
     </row>
     <row r="833">
       <c r="A833" t="n">
-        <v>1824</v>
+        <v>2423</v>
       </c>
       <c r="B833" t="n">
         <v>1</v>
@@ -9599,7 +9587,7 @@
     </row>
     <row r="834">
       <c r="A834" t="n">
-        <v>1823</v>
+        <v>2654</v>
       </c>
       <c r="B834" t="n">
         <v>1</v>
@@ -9610,7 +9598,7 @@
     </row>
     <row r="835">
       <c r="A835" t="n">
-        <v>1822</v>
+        <v>2655</v>
       </c>
       <c r="B835" t="n">
         <v>1</v>
@@ -9621,10 +9609,10 @@
     </row>
     <row r="836">
       <c r="A836" t="n">
-        <v>1419</v>
+        <v>2656</v>
       </c>
       <c r="B836" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C836" t="n">
         <v>0.2127659574468085</v>
@@ -9632,7 +9620,7 @@
     </row>
     <row r="837">
       <c r="A837" t="n">
-        <v>1819</v>
+        <v>2657</v>
       </c>
       <c r="B837" t="n">
         <v>1</v>
@@ -9643,10 +9631,10 @@
     </row>
     <row r="838">
       <c r="A838" t="n">
-        <v>1818</v>
+        <v>2659</v>
       </c>
       <c r="B838" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C838" t="n">
         <v>0.2127659574468085</v>
@@ -9654,7 +9642,7 @@
     </row>
     <row r="839">
       <c r="A839" t="n">
-        <v>1817</v>
+        <v>2660</v>
       </c>
       <c r="B839" t="n">
         <v>1</v>
@@ -9665,7 +9653,7 @@
     </row>
     <row r="840">
       <c r="A840" t="n">
-        <v>1815</v>
+        <v>2663</v>
       </c>
       <c r="B840" t="n">
         <v>1</v>
@@ -9676,7 +9664,7 @@
     </row>
     <row r="841">
       <c r="A841" t="n">
-        <v>1653</v>
+        <v>1596</v>
       </c>
       <c r="B841" t="n">
         <v>1</v>
@@ -9687,10 +9675,10 @@
     </row>
     <row r="842">
       <c r="A842" t="n">
-        <v>1813</v>
+        <v>1598</v>
       </c>
       <c r="B842" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C842" t="n">
         <v>0.2127659574468085</v>
@@ -9698,7 +9686,7 @@
     </row>
     <row r="843">
       <c r="A843" t="n">
-        <v>1812</v>
+        <v>2104</v>
       </c>
       <c r="B843" t="n">
         <v>1</v>
@@ -9709,7 +9697,7 @@
     </row>
     <row r="844">
       <c r="A844" t="n">
-        <v>1811</v>
+        <v>2667</v>
       </c>
       <c r="B844" t="n">
         <v>1</v>
@@ -9720,7 +9708,7 @@
     </row>
     <row r="845">
       <c r="A845" t="n">
-        <v>1832</v>
+        <v>2668</v>
       </c>
       <c r="B845" t="n">
         <v>1</v>
@@ -9731,7 +9719,7 @@
     </row>
     <row r="846">
       <c r="A846" t="n">
-        <v>1833</v>
+        <v>2669</v>
       </c>
       <c r="B846" t="n">
         <v>1</v>
@@ -9742,10 +9730,10 @@
     </row>
     <row r="847">
       <c r="A847" t="n">
-        <v>1647</v>
+        <v>2670</v>
       </c>
       <c r="B847" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C847" t="n">
         <v>0.2127659574468085</v>
@@ -9753,10 +9741,10 @@
     </row>
     <row r="848">
       <c r="A848" t="n">
-        <v>1421</v>
+        <v>2672</v>
       </c>
       <c r="B848" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C848" t="n">
         <v>0.2127659574468085</v>
@@ -9764,10 +9752,10 @@
     </row>
     <row r="849">
       <c r="A849" t="n">
-        <v>1905</v>
+        <v>2673</v>
       </c>
       <c r="B849" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C849" t="n">
         <v>0.2127659574468085</v>
@@ -9775,7 +9763,7 @@
     </row>
     <row r="850">
       <c r="A850" t="n">
-        <v>1904</v>
+        <v>2677</v>
       </c>
       <c r="B850" t="n">
         <v>1</v>
@@ -9786,7 +9774,7 @@
     </row>
     <row r="851">
       <c r="A851" t="n">
-        <v>1900</v>
+        <v>2678</v>
       </c>
       <c r="B851" t="n">
         <v>1</v>
@@ -9797,7 +9785,7 @@
     </row>
     <row r="852">
       <c r="A852" t="n">
-        <v>1895</v>
+        <v>2679</v>
       </c>
       <c r="B852" t="n">
         <v>1</v>
@@ -9808,10 +9796,10 @@
     </row>
     <row r="853">
       <c r="A853" t="n">
-        <v>1858</v>
+        <v>2681</v>
       </c>
       <c r="B853" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C853" t="n">
         <v>0.2127659574468085</v>
@@ -9819,7 +9807,7 @@
     </row>
     <row r="854">
       <c r="A854" t="n">
-        <v>1857</v>
+        <v>2683</v>
       </c>
       <c r="B854" t="n">
         <v>1</v>
@@ -9830,7 +9818,7 @@
     </row>
     <row r="855">
       <c r="A855" t="n">
-        <v>1854</v>
+        <v>2686</v>
       </c>
       <c r="B855" t="n">
         <v>1</v>
@@ -9841,7 +9829,7 @@
     </row>
     <row r="856">
       <c r="A856" t="n">
-        <v>1835</v>
+        <v>2688</v>
       </c>
       <c r="B856" t="n">
         <v>1</v>
@@ -9852,10 +9840,10 @@
     </row>
     <row r="857">
       <c r="A857" t="n">
-        <v>1845</v>
+        <v>1517</v>
       </c>
       <c r="B857" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C857" t="n">
         <v>0.2127659574468085</v>
@@ -9863,10 +9851,10 @@
     </row>
     <row r="858">
       <c r="A858" t="n">
-        <v>1843</v>
+        <v>1518</v>
       </c>
       <c r="B858" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C858" t="n">
         <v>0.2127659574468085</v>
@@ -9874,10 +9862,10 @@
     </row>
     <row r="859">
       <c r="A859" t="n">
-        <v>1842</v>
+        <v>1533</v>
       </c>
       <c r="B859" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C859" t="n">
         <v>0.2127659574468085</v>
@@ -9885,10 +9873,10 @@
     </row>
     <row r="860">
       <c r="A860" t="n">
-        <v>1841</v>
+        <v>1522</v>
       </c>
       <c r="B860" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C860" t="n">
         <v>0.2127659574468085</v>
@@ -9896,10 +9884,10 @@
     </row>
     <row r="861">
       <c r="A861" t="n">
-        <v>1838</v>
+        <v>1527</v>
       </c>
       <c r="B861" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C861" t="n">
         <v>0.2127659574468085</v>
@@ -9907,10 +9895,10 @@
     </row>
     <row r="862">
       <c r="A862" t="n">
-        <v>1836</v>
+        <v>1497</v>
       </c>
       <c r="B862" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C862" t="n">
         <v>0.2127659574468085</v>
@@ -9918,10 +9906,10 @@
     </row>
     <row r="863">
       <c r="A863" t="n">
-        <v>1809</v>
+        <v>1498</v>
       </c>
       <c r="B863" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C863" t="n">
         <v>0.2127659574468085</v>
@@ -9929,10 +9917,10 @@
     </row>
     <row r="864">
       <c r="A864" t="n">
-        <v>1808</v>
+        <v>1499</v>
       </c>
       <c r="B864" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C864" t="n">
         <v>0.2127659574468085</v>
@@ -9940,10 +9928,10 @@
     </row>
     <row r="865">
       <c r="A865" t="n">
-        <v>1807</v>
+        <v>1500</v>
       </c>
       <c r="B865" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C865" t="n">
         <v>0.2127659574468085</v>
@@ -9951,7 +9939,7 @@
     </row>
     <row r="866">
       <c r="A866" t="n">
-        <v>1675</v>
+        <v>12</v>
       </c>
       <c r="B866" t="n">
         <v>1</v>
@@ -9962,10 +9950,10 @@
     </row>
     <row r="867">
       <c r="A867" t="n">
-        <v>1741</v>
+        <v>1505</v>
       </c>
       <c r="B867" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C867" t="n">
         <v>0.2127659574468085</v>
@@ -9973,10 +9961,10 @@
     </row>
     <row r="868">
       <c r="A868" t="n">
-        <v>1665</v>
+        <v>1510</v>
       </c>
       <c r="B868" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C868" t="n">
         <v>0.2127659574468085</v>
@@ -9984,7 +9972,7 @@
     </row>
     <row r="869">
       <c r="A869" t="n">
-        <v>1737</v>
+        <v>1513</v>
       </c>
       <c r="B869" t="n">
         <v>1</v>
@@ -9995,7 +9983,7 @@
     </row>
     <row r="870">
       <c r="A870" t="n">
-        <v>1670</v>
+        <v>2690</v>
       </c>
       <c r="B870" t="n">
         <v>1</v>
@@ -10006,10 +9994,10 @@
     </row>
     <row r="871">
       <c r="A871" t="n">
-        <v>1671</v>
+        <v>2694</v>
       </c>
       <c r="B871" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C871" t="n">
         <v>0.2127659574468085</v>
@@ -10017,7 +10005,7 @@
     </row>
     <row r="872">
       <c r="A872" t="n">
-        <v>1733</v>
+        <v>2701</v>
       </c>
       <c r="B872" t="n">
         <v>1</v>
@@ -10028,7 +10016,7 @@
     </row>
     <row r="873">
       <c r="A873" t="n">
-        <v>1714</v>
+        <v>2703</v>
       </c>
       <c r="B873" t="n">
         <v>1</v>
@@ -10039,7 +10027,7 @@
     </row>
     <row r="874">
       <c r="A874" t="n">
-        <v>1748</v>
+        <v>2705</v>
       </c>
       <c r="B874" t="n">
         <v>1</v>
@@ -10050,7 +10038,7 @@
     </row>
     <row r="875">
       <c r="A875" t="n">
-        <v>1676</v>
+        <v>2665</v>
       </c>
       <c r="B875" t="n">
         <v>1</v>
@@ -10061,7 +10049,7 @@
     </row>
     <row r="876">
       <c r="A876" t="n">
-        <v>1679</v>
+        <v>2729</v>
       </c>
       <c r="B876" t="n">
         <v>1</v>
@@ -10072,7 +10060,7 @@
     </row>
     <row r="877">
       <c r="A877" t="n">
-        <v>1681</v>
+        <v>2739</v>
       </c>
       <c r="B877" t="n">
         <v>1</v>
@@ -10083,7 +10071,7 @@
     </row>
     <row r="878">
       <c r="A878" t="n">
-        <v>1708</v>
+        <v>3785</v>
       </c>
       <c r="B878" t="n">
         <v>1</v>
@@ -10094,7 +10082,7 @@
     </row>
     <row r="879">
       <c r="A879" t="n">
-        <v>1686</v>
+        <v>3787</v>
       </c>
       <c r="B879" t="n">
         <v>1</v>
@@ -10105,10 +10093,10 @@
     </row>
     <row r="880">
       <c r="A880" t="n">
-        <v>1688</v>
+        <v>3792</v>
       </c>
       <c r="B880" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C880" t="n">
         <v>0.2127659574468085</v>
@@ -10116,7 +10104,7 @@
     </row>
     <row r="881">
       <c r="A881" t="n">
-        <v>1746</v>
+        <v>3797</v>
       </c>
       <c r="B881" t="n">
         <v>1</v>
@@ -10127,7 +10115,7 @@
     </row>
     <row r="882">
       <c r="A882" t="n">
-        <v>1753</v>
+        <v>3803</v>
       </c>
       <c r="B882" t="n">
         <v>1</v>
@@ -10138,7 +10126,7 @@
     </row>
     <row r="883">
       <c r="A883" t="n">
-        <v>1806</v>
+        <v>3806</v>
       </c>
       <c r="B883" t="n">
         <v>1</v>
@@ -10149,7 +10137,7 @@
     </row>
     <row r="884">
       <c r="A884" t="n">
-        <v>1655</v>
+        <v>3809</v>
       </c>
       <c r="B884" t="n">
         <v>1</v>
@@ -10160,10 +10148,10 @@
     </row>
     <row r="885">
       <c r="A885" t="n">
-        <v>1804</v>
+        <v>3810</v>
       </c>
       <c r="B885" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C885" t="n">
         <v>0.2127659574468085</v>
@@ -10171,7 +10159,7 @@
     </row>
     <row r="886">
       <c r="A886" t="n">
-        <v>1803</v>
+        <v>3812</v>
       </c>
       <c r="B886" t="n">
         <v>1</v>
@@ -10182,7 +10170,7 @@
     </row>
     <row r="887">
       <c r="A887" t="n">
-        <v>1802</v>
+        <v>3821</v>
       </c>
       <c r="B887" t="n">
         <v>1</v>
@@ -10193,7 +10181,7 @@
     </row>
     <row r="888">
       <c r="A888" t="n">
-        <v>1801</v>
+        <v>3829</v>
       </c>
       <c r="B888" t="n">
         <v>1</v>
@@ -10204,7 +10192,7 @@
     </row>
     <row r="889">
       <c r="A889" t="n">
-        <v>1797</v>
+        <v>3833</v>
       </c>
       <c r="B889" t="n">
         <v>1</v>
@@ -10215,7 +10203,7 @@
     </row>
     <row r="890">
       <c r="A890" t="n">
-        <v>1796</v>
+        <v>3834</v>
       </c>
       <c r="B890" t="n">
         <v>1</v>
@@ -10226,10 +10214,10 @@
     </row>
     <row r="891">
       <c r="A891" t="n">
-        <v>1789</v>
+        <v>1519</v>
       </c>
       <c r="B891" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C891" t="n">
         <v>0.2127659574468085</v>
@@ -10237,7 +10225,7 @@
     </row>
     <row r="892">
       <c r="A892" t="n">
-        <v>1755</v>
+        <v>4353</v>
       </c>
       <c r="B892" t="n">
         <v>1</v>
@@ -10248,7 +10236,7 @@
     </row>
     <row r="893">
       <c r="A893" t="n">
-        <v>1657</v>
+        <v>4359</v>
       </c>
       <c r="B893" t="n">
         <v>1</v>
@@ -10259,7 +10247,7 @@
     </row>
     <row r="894">
       <c r="A894" t="n">
-        <v>1658</v>
+        <v>4360</v>
       </c>
       <c r="B894" t="n">
         <v>1</v>
@@ -10270,7 +10258,7 @@
     </row>
     <row r="895">
       <c r="A895" t="n">
-        <v>1661</v>
+        <v>4362</v>
       </c>
       <c r="B895" t="n">
         <v>1</v>
@@ -10281,10 +10269,10 @@
     </row>
     <row r="896">
       <c r="A896" t="n">
-        <v>1663</v>
+        <v>4374</v>
       </c>
       <c r="B896" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C896" t="n">
         <v>0.2127659574468085</v>
@@ -10292,7 +10280,7 @@
     </row>
     <row r="897">
       <c r="A897" t="n">
-        <v>1759</v>
+        <v>4376</v>
       </c>
       <c r="B897" t="n">
         <v>1</v>
@@ -10303,7 +10291,7 @@
     </row>
     <row r="898">
       <c r="A898" t="n">
-        <v>1758</v>
+        <v>4379</v>
       </c>
       <c r="B898" t="n">
         <v>1</v>
@@ -10314,7 +10302,7 @@
     </row>
     <row r="899">
       <c r="A899" t="n">
-        <v>2679</v>
+        <v>90</v>
       </c>
       <c r="B899" t="n">
         <v>1</v>
@@ -10325,7 +10313,7 @@
     </row>
     <row r="900">
       <c r="A900" t="n">
-        <v>1906</v>
+        <v>4387</v>
       </c>
       <c r="B900" t="n">
         <v>1</v>
@@ -10336,7 +10324,7 @@
     </row>
     <row r="901">
       <c r="A901" t="n">
-        <v>2016</v>
+        <v>4390</v>
       </c>
       <c r="B901" t="n">
         <v>1</v>
@@ -10347,10 +10335,10 @@
     </row>
     <row r="902">
       <c r="A902" t="n">
-        <v>1611</v>
+        <v>1481</v>
       </c>
       <c r="B902" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C902" t="n">
         <v>0.2127659574468085</v>
@@ -10358,10 +10346,10 @@
     </row>
     <row r="903">
       <c r="A903" t="n">
-        <v>2126</v>
+        <v>1483</v>
       </c>
       <c r="B903" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C903" t="n">
         <v>0.2127659574468085</v>
@@ -10369,10 +10357,10 @@
     </row>
     <row r="904">
       <c r="A904" t="n">
-        <v>2124</v>
+        <v>1484</v>
       </c>
       <c r="B904" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C904" t="n">
         <v>0.2127659574468085</v>
@@ -10380,10 +10368,10 @@
     </row>
     <row r="905">
       <c r="A905" t="n">
-        <v>2123</v>
+        <v>1487</v>
       </c>
       <c r="B905" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C905" t="n">
         <v>0.2127659574468085</v>
@@ -10391,7 +10379,7 @@
     </row>
     <row r="906">
       <c r="A906" t="n">
-        <v>2120</v>
+        <v>5468</v>
       </c>
       <c r="B906" t="n">
         <v>1</v>
@@ -10402,7 +10390,7 @@
     </row>
     <row r="907">
       <c r="A907" t="n">
-        <v>2118</v>
+        <v>2708</v>
       </c>
       <c r="B907" t="n">
         <v>1</v>
@@ -10413,7 +10401,7 @@
     </row>
     <row r="908">
       <c r="A908" t="n">
-        <v>2112</v>
+        <v>5284</v>
       </c>
       <c r="B908" t="n">
         <v>1</v>
@@ -10424,7 +10412,7 @@
     </row>
     <row r="909">
       <c r="A909" t="n">
-        <v>2110</v>
+        <v>1469</v>
       </c>
       <c r="B909" t="n">
         <v>1</v>
@@ -10435,7 +10423,7 @@
     </row>
     <row r="910">
       <c r="A910" t="n">
-        <v>2109</v>
+        <v>1477</v>
       </c>
       <c r="B910" t="n">
         <v>1</v>
@@ -10446,10 +10434,10 @@
     </row>
     <row r="911">
       <c r="A911" t="n">
-        <v>2108</v>
+        <v>1466</v>
       </c>
       <c r="B911" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C911" t="n">
         <v>0.2127659574468085</v>
@@ -10457,10 +10445,10 @@
     </row>
     <row r="912">
       <c r="A912" t="n">
-        <v>2104</v>
+        <v>5285</v>
       </c>
       <c r="B912" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C912" t="n">
         <v>0.2127659574468085</v>
@@ -10468,7 +10456,7 @@
     </row>
     <row r="913">
       <c r="A913" t="n">
-        <v>2099</v>
+        <v>5286</v>
       </c>
       <c r="B913" t="n">
         <v>1</v>
@@ -10479,7 +10467,7 @@
     </row>
     <row r="914">
       <c r="A914" t="n">
-        <v>2097</v>
+        <v>4396</v>
       </c>
       <c r="B914" t="n">
         <v>1</v>
@@ -10490,7 +10478,7 @@
     </row>
     <row r="915">
       <c r="A915" t="n">
-        <v>1613</v>
+        <v>4397</v>
       </c>
       <c r="B915" t="n">
         <v>1</v>
@@ -10501,7 +10489,7 @@
     </row>
     <row r="916">
       <c r="A916" t="n">
-        <v>2094</v>
+        <v>4399</v>
       </c>
       <c r="B916" t="n">
         <v>1</v>
@@ -10512,7 +10500,7 @@
     </row>
     <row r="917">
       <c r="A917" t="n">
-        <v>2023</v>
+        <v>4400</v>
       </c>
       <c r="B917" t="n">
         <v>1</v>
@@ -10523,7 +10511,7 @@
     </row>
     <row r="918">
       <c r="A918" t="n">
-        <v>2129</v>
+        <v>4402</v>
       </c>
       <c r="B918" t="n">
         <v>1</v>
@@ -10534,7 +10522,7 @@
     </row>
     <row r="919">
       <c r="A919" t="n">
-        <v>2423</v>
+        <v>4407</v>
       </c>
       <c r="B919" t="n">
         <v>1</v>
@@ -10545,7 +10533,7 @@
     </row>
     <row r="920">
       <c r="A920" t="n">
-        <v>2017</v>
+        <v>4413</v>
       </c>
       <c r="B920" t="n">
         <v>1</v>
@@ -10556,7 +10544,7 @@
     </row>
     <row r="921">
       <c r="A921" t="n">
-        <v>1477</v>
+        <v>4416</v>
       </c>
       <c r="B921" t="n">
         <v>1</v>
@@ -10567,7 +10555,7 @@
     </row>
     <row r="922">
       <c r="A922" t="n">
-        <v>2678</v>
+        <v>457</v>
       </c>
       <c r="B922" t="n">
         <v>1</v>
@@ -10578,7 +10566,7 @@
     </row>
     <row r="923">
       <c r="A923" t="n">
-        <v>2677</v>
+        <v>4102</v>
       </c>
       <c r="B923" t="n">
         <v>1</v>
@@ -10589,7 +10577,7 @@
     </row>
     <row r="924">
       <c r="A924" t="n">
-        <v>2673</v>
+        <v>619</v>
       </c>
       <c r="B924" t="n">
         <v>1</v>
@@ -10600,7 +10588,7 @@
     </row>
     <row r="925">
       <c r="A925" t="n">
-        <v>2672</v>
+        <v>860</v>
       </c>
       <c r="B925" t="n">
         <v>1</v>
@@ -10611,7 +10599,7 @@
     </row>
     <row r="926">
       <c r="A926" t="n">
-        <v>2670</v>
+        <v>1010</v>
       </c>
       <c r="B926" t="n">
         <v>1</v>
@@ -10622,7 +10610,7 @@
     </row>
     <row r="927">
       <c r="A927" t="n">
-        <v>2669</v>
+        <v>1069</v>
       </c>
       <c r="B927" t="n">
         <v>1</v>
@@ -10633,7 +10621,7 @@
     </row>
     <row r="928">
       <c r="A928" t="n">
-        <v>2668</v>
+        <v>1112</v>
       </c>
       <c r="B928" t="n">
         <v>1</v>
@@ -10644,7 +10632,7 @@
     </row>
     <row r="929">
       <c r="A929" t="n">
-        <v>2667</v>
+        <v>1113</v>
       </c>
       <c r="B929" t="n">
         <v>1</v>
@@ -10655,7 +10643,7 @@
     </row>
     <row r="930">
       <c r="A930" t="n">
-        <v>2665</v>
+        <v>1114</v>
       </c>
       <c r="B930" t="n">
         <v>1</v>
@@ -10666,7 +10654,7 @@
     </row>
     <row r="931">
       <c r="A931" t="n">
-        <v>2663</v>
+        <v>438</v>
       </c>
       <c r="B931" t="n">
         <v>1</v>
@@ -10677,7 +10665,7 @@
     </row>
     <row r="932">
       <c r="A932" t="n">
-        <v>2660</v>
+        <v>5108</v>
       </c>
       <c r="B932" t="n">
         <v>1</v>
@@ -10688,7 +10676,7 @@
     </row>
     <row r="933">
       <c r="A933" t="n">
-        <v>2659</v>
+        <v>5169</v>
       </c>
       <c r="B933" t="n">
         <v>1</v>
@@ -10699,7 +10687,7 @@
     </row>
     <row r="934">
       <c r="A934" t="n">
-        <v>2656</v>
+        <v>5242</v>
       </c>
       <c r="B934" t="n">
         <v>1</v>
@@ -10710,7 +10698,7 @@
     </row>
     <row r="935">
       <c r="A935" t="n">
-        <v>2655</v>
+        <v>4382</v>
       </c>
       <c r="B935" t="n">
         <v>1</v>
@@ -10721,7 +10709,7 @@
     </row>
     <row r="936">
       <c r="A936" t="n">
-        <v>2654</v>
+        <v>5287</v>
       </c>
       <c r="B936" t="n">
         <v>1</v>
@@ -10732,10 +10720,10 @@
     </row>
     <row r="937">
       <c r="A937" t="n">
-        <v>2018</v>
+        <v>1419</v>
       </c>
       <c r="B937" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C937" t="n">
         <v>0.2127659574468085</v>
@@ -10743,7 +10731,7 @@
     </row>
     <row r="938">
       <c r="A938" t="n">
-        <v>20295</v>
+        <v>5288</v>
       </c>
       <c r="B938" t="n">
         <v>1</v>
@@ -10754,10 +10742,10 @@
     </row>
     <row r="939">
       <c r="A939" t="n">
-        <v>1909</v>
+        <v>1421</v>
       </c>
       <c r="B939" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C939" t="n">
         <v>0.2127659574468085</v>
@@ -10765,10 +10753,10 @@
     </row>
     <row r="940">
       <c r="A940" t="n">
-        <v>1637</v>
+        <v>5282</v>
       </c>
       <c r="B940" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C940" t="n">
         <v>0.2127659574468085</v>
@@ -10776,7 +10764,7 @@
     </row>
     <row r="941">
       <c r="A941" t="n">
-        <v>1935</v>
+        <v>5289</v>
       </c>
       <c r="B941" t="n">
         <v>1</v>
@@ -10787,10 +10775,10 @@
     </row>
     <row r="942">
       <c r="A942" t="n">
-        <v>1933</v>
+        <v>5317</v>
       </c>
       <c r="B942" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C942" t="n">
         <v>0.2127659574468085</v>
@@ -10798,7 +10786,7 @@
     </row>
     <row r="943">
       <c r="A943" t="n">
-        <v>1932</v>
+        <v>197</v>
       </c>
       <c r="B943" t="n">
         <v>1</v>
@@ -10809,7 +10797,7 @@
     </row>
     <row r="944">
       <c r="A944" t="n">
-        <v>1931</v>
+        <v>236</v>
       </c>
       <c r="B944" t="n">
         <v>1</v>
@@ -10820,7 +10808,7 @@
     </row>
     <row r="945">
       <c r="A945" t="n">
-        <v>1928</v>
+        <v>276</v>
       </c>
       <c r="B945" t="n">
         <v>1</v>
@@ -10831,7 +10819,7 @@
     </row>
     <row r="946">
       <c r="A946" t="n">
-        <v>1636</v>
+        <v>372</v>
       </c>
       <c r="B946" t="n">
         <v>1</v>
@@ -10842,10 +10830,10 @@
     </row>
     <row r="947">
       <c r="A947" t="n">
-        <v>1639</v>
+        <v>390</v>
       </c>
       <c r="B947" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C947" t="n">
         <v>0.2127659574468085</v>
@@ -10853,10 +10841,10 @@
     </row>
     <row r="948">
       <c r="A948" t="n">
-        <v>1941</v>
+        <v>401</v>
       </c>
       <c r="B948" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C948" t="n">
         <v>0.2127659574468085</v>
@@ -10864,10 +10852,10 @@
     </row>
     <row r="949">
       <c r="A949" t="n">
-        <v>1920</v>
+        <v>419</v>
       </c>
       <c r="B949" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C949" t="n">
         <v>0.2127659574468085</v>
@@ -10875,7 +10863,7 @@
     </row>
     <row r="950">
       <c r="A950" t="n">
-        <v>1918</v>
+        <v>128</v>
       </c>
       <c r="B950" t="n">
         <v>1</v>
@@ -10886,7 +10874,7 @@
     </row>
     <row r="951">
       <c r="A951" t="n">
-        <v>1916</v>
+        <v>139</v>
       </c>
       <c r="B951" t="n">
         <v>1</v>
@@ -10897,10 +10885,10 @@
     </row>
     <row r="952">
       <c r="A952" t="n">
-        <v>1914</v>
+        <v>5424</v>
       </c>
       <c r="B952" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C952" t="n">
         <v>0.2127659574468085</v>
@@ -10908,7 +10896,7 @@
     </row>
     <row r="953">
       <c r="A953" t="n">
-        <v>1913</v>
+        <v>5442</v>
       </c>
       <c r="B953" t="n">
         <v>1</v>
@@ -10919,7 +10907,7 @@
     </row>
     <row r="954">
       <c r="A954" t="n">
-        <v>1912</v>
+        <v>5446</v>
       </c>
       <c r="B954" t="n">
         <v>1</v>
@@ -10930,7 +10918,7 @@
     </row>
     <row r="955">
       <c r="A955" t="n">
-        <v>2015</v>
+        <v>52</v>
       </c>
       <c r="B955" t="n">
         <v>1</v>
@@ -10941,7 +10929,7 @@
     </row>
     <row r="956">
       <c r="A956" t="n">
-        <v>1939</v>
+        <v>5356</v>
       </c>
       <c r="B956" t="n">
         <v>1</v>
@@ -10952,7 +10940,7 @@
     </row>
     <row r="957">
       <c r="A957" t="n">
-        <v>1943</v>
+        <v>5503</v>
       </c>
       <c r="B957" t="n">
         <v>1</v>
@@ -10963,10 +10951,10 @@
     </row>
     <row r="958">
       <c r="A958" t="n">
-        <v>1947</v>
+        <v>5447</v>
       </c>
       <c r="B958" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C958" t="n">
         <v>0.2127659574468085</v>
@@ -10974,7 +10962,7 @@
     </row>
     <row r="959">
       <c r="A959" t="n">
-        <v>1469</v>
+        <v>11920</v>
       </c>
       <c r="B959" t="n">
         <v>1</v>
@@ -10985,10 +10973,10 @@
     </row>
     <row r="960">
       <c r="A960" t="n">
-        <v>1466</v>
+        <v>11990</v>
       </c>
       <c r="B960" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C960" t="n">
         <v>0.2127659574468085</v>
@@ -10996,7 +10984,7 @@
     </row>
     <row r="961">
       <c r="A961" t="n">
-        <v>1617</v>
+        <v>11993</v>
       </c>
       <c r="B961" t="n">
         <v>1</v>
@@ -11007,7 +10995,7 @@
     </row>
     <row r="962">
       <c r="A962" t="n">
-        <v>1620</v>
+        <v>11996</v>
       </c>
       <c r="B962" t="n">
         <v>1</v>
@@ -11018,7 +11006,7 @@
     </row>
     <row r="963">
       <c r="A963" t="n">
-        <v>1964</v>
+        <v>10</v>
       </c>
       <c r="B963" t="n">
         <v>1</v>
@@ -11029,10 +11017,10 @@
     </row>
     <row r="964">
       <c r="A964" t="n">
-        <v>1625</v>
+        <v>11998</v>
       </c>
       <c r="B964" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C964" t="n">
         <v>0.2127659574468085</v>
@@ -11040,7 +11028,7 @@
     </row>
     <row r="965">
       <c r="A965" t="n">
-        <v>1960</v>
+        <v>11999</v>
       </c>
       <c r="B965" t="n">
         <v>1</v>
@@ -11051,7 +11039,7 @@
     </row>
     <row r="966">
       <c r="A966" t="n">
-        <v>1959</v>
+        <v>20220</v>
       </c>
       <c r="B966" t="n">
         <v>1</v>
@@ -11062,7 +11050,7 @@
     </row>
     <row r="967">
       <c r="A967" t="n">
-        <v>1627</v>
+        <v>1714</v>
       </c>
       <c r="B967" t="n">
         <v>1</v>
@@ -11073,7 +11061,7 @@
     </row>
     <row r="968">
       <c r="A968" t="n">
-        <v>1956</v>
+        <v>1733</v>
       </c>
       <c r="B968" t="n">
         <v>1</v>
@@ -11084,10 +11072,10 @@
     </row>
     <row r="969">
       <c r="A969" t="n">
-        <v>1313</v>
+        <v>1737</v>
       </c>
       <c r="B969" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C969" t="n">
         <v>0.2127659574468085</v>
@@ -11095,7 +11083,7 @@
     </row>
     <row r="970">
       <c r="A970" t="n">
-        <v>1954</v>
+        <v>1741</v>
       </c>
       <c r="B970" t="n">
         <v>1</v>
@@ -11106,7 +11094,7 @@
     </row>
     <row r="971">
       <c r="A971" t="n">
-        <v>1630</v>
+        <v>20295</v>
       </c>
       <c r="B971" t="n">
         <v>1</v>
